--- a/catastro_vehiculos_transformado.xlsx
+++ b/catastro_vehiculos_transformado.xlsx
@@ -2124,7 +2124,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Camioneta 4X2</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">CAMIONETA </t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">CAMIONETA </t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">CAMIONETA </t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve"> Station Wagon</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve"> Station Wagon</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve"> Station Wagon</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve"> Station Wagon</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>camioneta</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Camioneta 4X2</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Station wagon</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Station wagon</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Station wagon</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Camion</t>
+          <t>CAMION</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Minibus</t>
+          <t>MINIBUS</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -7918,7 +7918,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PGC 2026 - pendiente</t>
+          <t>PGC 2026-Serviu-en proceso de compra</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">STATION WAGON </t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">Station Wagon </t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">Station Wagon </t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">Station Wagon </t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">Camioneta </t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">Station Wagon </t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">Station Wagon </t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">Station Wagon </t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t xml:space="preserve">Station Wagon </t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -9890,7 +9890,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PGC 2026 - pendiente</t>
+          <t>PGC 2026-Serviu-en proceso de compra</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -10085,7 +10085,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PGC 2026 - pendiente</t>
+          <t>PGC 2026-Serviu-en proceso de compra</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Minibus</t>
+          <t>MINIBUS</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">Camioneta </t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">Camioneta </t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">Camioneta </t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">Camioneta </t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Minibus</t>
+          <t>MINIBUS</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Minibus</t>
+          <t>MINIBUS</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Minibus</t>
+          <t>MINIBUS</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Camioneta 4X2</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -14402,7 +14402,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PGC 2026 - pendiente</t>
+          <t>PGC 2026-Serviu-en proceso de compra</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>CAMIONETA</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">CAMIONETA </t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -19567,7 +19567,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Minibus</t>
+          <t xml:space="preserve">MINI BUS </t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t xml:space="preserve">CAMIIONETA </t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Station wagon</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Station wagon</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -20858,7 +20858,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Station wagon</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -21119,7 +21119,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F226" t="n">

--- a/catastro_vehiculos_transformado.xlsx
+++ b/catastro_vehiculos_transformado.xlsx
@@ -12353,7 +12353,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PGC 2026 - pendiente</t>
+          <t>PGC 2026-Serviu-en proceso de compra</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -19010,10 +19010,20 @@
       <c r="F202" t="n">
         <v>2026</v>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
+      <c r="G202" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H202" t="n">
+        <v>273756</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Híbrido</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>18</v>
+      </c>
       <c r="K202" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -19067,7 +19077,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PGC 2026 -pendiente</t>
+        </is>
+      </c>
       <c r="B203" t="n">
         <v>203</v>
       </c>
@@ -19090,10 +19104,10 @@
         <v>2018</v>
       </c>
       <c r="G203" t="n">
-        <v>277774</v>
+        <v>300000</v>
       </c>
       <c r="H203" t="n">
-        <v>7310131</v>
+        <v>8637487</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -19101,7 +19115,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -19110,13 +19124,17 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M203" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Problemas en Radiador y Caliper</t>
+        </is>
+      </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Además de las mantenciones normales, se realizó el cambio del radiador, debido a que la fuga de líquido refrigerante estaba escurriendo hacia el piso del vehículo, específicamente bajo el asiento del conductor</t>
+          <t>8 AÑOS DE USO, se sugiere reemplazo por vehiculo cerrado (de preferencia SUV) ha presentando fallas en el radiador de calefaccion en varias ocaciones, generando un gasto mas alto en reparaciones.</t>
         </is>
       </c>
       <c r="O203" t="inlineStr"/>
@@ -19127,7 +19145,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -19141,11 +19159,11 @@
         </is>
       </c>
       <c r="T203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
@@ -19183,10 +19201,10 @@
         <v>2019</v>
       </c>
       <c r="G204" t="n">
-        <v>207341</v>
+        <v>230000</v>
       </c>
       <c r="H204" t="n">
-        <v>10585203</v>
+        <v>12150862</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -19194,7 +19212,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -19203,15 +19221,17 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>ANTIGÜEDAD DE USO</t>
+        </is>
+      </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Además de las mantenciones habituales, solo se realizaron las siguientes intervenciones:
-Revisión del sistema de refrigeración y prueba hidráulica.
-Cambio de la tapa del depósito de agua</t>
+          <t xml:space="preserve">8 AÑOS DE USO, se sugiere reemplazo por vehiculo cerrado (de preferencia SUV) </t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -19226,7 +19246,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -19240,11 +19260,11 @@
         </is>
       </c>
       <c r="T204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
@@ -19282,10 +19302,10 @@
         <v>2023</v>
       </c>
       <c r="G205" t="n">
-        <v>58781</v>
+        <v>60000</v>
       </c>
       <c r="H205" t="n">
-        <v>2575357</v>
+        <v>3343658</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -19302,13 +19322,17 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>NO APTO PARA LA REGION</t>
+        </is>
+      </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>El vehiculo tiene poco uso por su estructura, no sirve mucho para una zona de mucha lluvia.</t>
+          <t>Tipo de vehículo NO Apto para la Region, se pierde la parte trasera del vehículo, no se pueden dejar cosas o trasladar, si esta lloviendo, se necesita un vehículo cerrado.</t>
         </is>
       </c>
       <c r="O205" t="inlineStr"/>
@@ -19319,7 +19343,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -19333,7 +19357,7 @@
         </is>
       </c>
       <c r="T205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
@@ -19375,10 +19399,10 @@
         <v>2025</v>
       </c>
       <c r="G206" t="n">
-        <v>16075</v>
+        <v>30000</v>
       </c>
       <c r="H206" t="n">
-        <v>279990</v>
+        <v>1437583</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -19386,7 +19410,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -19399,11 +19423,7 @@
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vehículo adquirido en el presenta año, solo tiene una mantencion </t>
-        </is>
-      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
@@ -21501,7 +21521,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -21516,7 +21536,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/catastro_vehiculos_transformado.xlsx
+++ b/catastro_vehiculos_transformado.xlsx
@@ -8751,8 +8751,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>2031</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PGC2026-pendiente</t>
+        </is>
       </c>
       <c r="B89" t="n">
         <v>88</v>
@@ -8769,17 +8771,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>MINIBUS</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>2017</v>
       </c>
       <c r="G89" t="n">
-        <v>324845</v>
+        <v>355791</v>
       </c>
       <c r="H89" t="n">
-        <v>13359176</v>
+        <v>16532249</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8787,7 +8789,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -8796,13 +8798,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Sistema de aire acondicionado presenta falla general de funcionamiento, además requiere efectuar diagnóstico y revisión integral del motor, verificando su estado general y posibles desgastes asociados al uso. Considerar revisión de compresión, posibles fugas de aceite y refrigerante, sistema de inyección, inyectores, turbo, correas y tensores, sistema de refrigeración, soportes de motor, emisiones, ruidos y vibraciones anormales.</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>antigüedad.Minibus (no tiene urgencia de renovacion PRO)</t>
+          <t>Vehículo con 9 años de antigüedad y más de 355 mil km, destinado al Pool Vehicular y, por tanto, sometido a uso frecuente. Su alto kilometraje incrementa la probabilidad de reparaciones correctivas y recambio de componentes de alto costo, además de períodos de indisponibilidad. Su renovación permitiría mejorar la confiabilidad operacional, seguridad y continuidad del servicio.</t>
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
@@ -8813,7 +8819,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8827,11 +8833,11 @@
         </is>
       </c>
       <c r="T89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8862,17 +8868,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Station Wagon </t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>2019</v>
       </c>
       <c r="G90" t="n">
-        <v>245705</v>
+        <v>261904</v>
       </c>
       <c r="H90" t="n">
-        <v>13813610</v>
+        <v>13693018</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8958,10 +8964,10 @@
         <v>2025</v>
       </c>
       <c r="G91" t="n">
-        <v>15256</v>
+        <v>45213</v>
       </c>
       <c r="H91" t="n">
-        <v>1034291</v>
+        <v>1160251</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -9037,22 +9043,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>HTLH46</t>
+          <t>LVDS61</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Station Wagon </t>
+          <t>Van</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="G92" t="n">
-        <v>230543</v>
+        <v>210756</v>
       </c>
       <c r="H92" t="n">
-        <v>17041314</v>
+        <v>27071968</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -9069,28 +9075,20 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Saturación DPF</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>Antigüedad</t>
-        </is>
-      </c>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -9104,11 +9102,11 @@
         </is>
       </c>
       <c r="T92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9123,8 +9121,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
-        <v>2028</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PGC2026-pendiente</t>
+        </is>
       </c>
       <c r="B93" t="n">
         <v>92</v>
@@ -9141,17 +9141,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Station Wagon </t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>2018</v>
       </c>
       <c r="G93" t="n">
-        <v>218760</v>
+        <v>235338</v>
       </c>
       <c r="H93" t="n">
-        <v>11053404</v>
+        <v>11448848</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -9168,13 +9168,17 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Desgaste por kilometraje</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>Vehículo con 8 años de antigüedad y más de 235 mil km. El kilometraje acumulado hace recomendable planificar su renovación, considerando el desgaste progresivo de componentes y el aumento esperado de los costos de mantenimiento.</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
@@ -9185,7 +9189,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -9199,11 +9203,11 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9234,14 +9238,14 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camioneta </t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>2024</v>
       </c>
       <c r="G94" t="n">
-        <v>86970</v>
+        <v>105736</v>
       </c>
       <c r="H94" t="n">
         <v>3322045</v>
@@ -9252,7 +9256,7 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -9284,11 +9288,11 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -9323,14 +9327,14 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Station Wagon </t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>2024</v>
       </c>
       <c r="G95" t="n">
-        <v>62691</v>
+        <v>80096</v>
       </c>
       <c r="H95" t="n">
         <v>2772881</v>
@@ -9341,7 +9345,7 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -9412,20 +9416,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Station Wagon </t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>2026</v>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>18491</v>
+      </c>
+      <c r="H96" t="n">
+        <v>695786</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>14</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No indica</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -9487,20 +9505,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Station Wagon </t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>2026</v>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>25226</v>
+      </c>
+      <c r="H97" t="n">
+        <v>643400</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>14</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No indica</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -9562,20 +9594,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Station Wagon </t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>2026</v>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="G98" t="n">
+        <v>15403</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1845258</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No indica</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -19079,7 +19125,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PGC 2026 -pendiente</t>
+          <t>PGC2026-pendiente</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -21521,7 +21567,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -21536,7 +21582,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -21550,7 +21596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22274,6 +22320,70 @@
       <c r="P10" t="inlineStr">
         <is>
           <t>VRFV91</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SERVIU Valparaíso</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HTLH.46-6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Station Wagon </t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="G11" t="n">
+        <v>230543</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17041314</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Saturación DPF</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Antigüedad</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>VSBB24</t>
         </is>
       </c>
     </row>

--- a/catastro_vehiculos_transformado.xlsx
+++ b/catastro_vehiculos_transformado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W227"/>
+  <dimension ref="A1:W226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,7 +561,7 @@
         <v>2011</v>
       </c>
       <c r="G2" t="n">
-        <v>289880</v>
+        <v>300166</v>
       </c>
       <c r="H2" t="n">
         <v>1733390</v>
@@ -592,7 +592,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere reemplazar el vehículo perteneciente a dirección, dado que este cuenta con desperfectos en el sistema de air bag, esto impide tener certeza del funcionamiento de este sistema, lo cual, puede atentar contra la seguridad de los usuarios, además de tener restricción vehiculas desde mayo a septiembre, lo que impide su utilización al menos un día a la semana, perjudicando la operación del parque en general, debido a que esta unidad debe ser reemplazada los días que no puede circular. </t>
+          <t>Reparada mediante contrato vigente, recepcion conforme.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -674,22 +674,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Comodato RM</t>
+          <t xml:space="preserve">inactivo </t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Falla volante de embrague.</t>
+          <t>Sensor  de presión combustible, kit de embrague. Inyectores, culata</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Se realizó por el contratista, rectificación del volante de motor. Vehiculo transferido por SERVIU RM por tanto no contamos con mayores antecedentes de gastos acumulados de mantención.</t>
+          <t>en taller</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>2014</v>
       </c>
       <c r="G4" t="n">
-        <v>87932</v>
+        <v>90841</v>
       </c>
       <c r="H4" t="n">
         <v>16868563</v>
@@ -781,12 +781,13 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Falla bomba de embrague - rodamiento hidraulico - kit de embrague - disco delanteros - radiador y Sist. electrico</t>
+          <t>Falla bomba de embrague - rodamiento hidráulico - kit de embrague - disco delanteros - radiador y Sistema eléctrico, tren delantero, bujes de paquete trasero.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Actualmente este mini bus requiere una renovación de manera urgente, presenta una falla en su sistema de inyección, el cual, genera problemas en la conducción, desencadenando una situación de riesgo para los pasajeros, esta falla ya ocasiono la baja de una unidad de iguales características. Se requiere contar con un vehículo de igual o mayor capacidad para el traslado de los funcionarios a su lugar de trabajo al interior del cerro, los costos de mantención y reparación de la unidad, junto con la escases de repuestos en el mercado, generan problemas para mantener la unidad al 100%.</t>
+          <t xml:space="preserve">Vehículo en mal estado se adjunta informe técnico. Actualmente este mini bus requiere una renovación de manera urgente, presenta una falla en su sistema de inyección, el cual, genera problemas en la conducción, desencadenando una situación de riesgo para los pasajeros, esta falla ya ocasiono la baja de una unidad de iguales características. Se requiere contar con un vehículo de igual o mayor capacidad para el traslado de los funcionarios a su lugar de trabajo al interior del cerro, los costos de mantención y reparación de la unidad, junto con la escases de repuestos en el mercado, generan problemas para mantener la unidad 
+</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -855,7 +856,7 @@
         <v>2015</v>
       </c>
       <c r="G5" t="n">
-        <v>212379</v>
+        <v>219398</v>
       </c>
       <c r="H5" t="n">
         <v>8663204</v>
@@ -880,12 +881,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>reparación de caja de cambio, cambio diferencial, trinquete de freno de estacionamiento, cambio discos de freno delanteros.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reparada, funcionando con recepcion conforme.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -954,7 +955,7 @@
         <v>2011</v>
       </c>
       <c r="G6" t="n">
-        <v>187934</v>
+        <v>191783</v>
       </c>
       <c r="H6" t="n">
         <v>27721376</v>
@@ -979,12 +980,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Falla sensor de presión combustible - electrica - inyectores - computador - motor.</t>
+          <t>Falla sensor de presión combustible - eléctrica - inyectores - computador - motor.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Es necesario considerar la renovación de esta unidad, dado los elevados costo de reparaciones y mantenciones de la unidad, al ser una unidad clave para la prevención de incendios y cuidados del las áreas forestales del parque. También es necesario realizar la evaluación del tipo de vehículo, considerando que al requerir una licencia profesional para su conducción, restringe mucho su uso. </t>
+          <t>Es necesario considerar la renovación de esta unidad, dado los elevados costo de reparaciones y mantenciones de la unidad, al ser una unidad clave para la prevención de incendios y cuidados del las áreas forestales del parque</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1051,7 +1052,7 @@
         <v>2016</v>
       </c>
       <c r="G7" t="n">
-        <v>268501</v>
+        <v>276131</v>
       </c>
       <c r="H7" t="n">
         <v>11817445</v>
@@ -1076,13 +1077,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falla en soporte delantero - bomba de agua - correa accesorios - carter -soporte diferencial - reten de cola cigüeñal - punta homocinetica.
-</t>
+          <t>Falla en soporte delantero - bomba de agua - correa accesorios - Carter -soporte diferencial - reten de cola cigüeñal - punta homocinética.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Se realizo por el contratista, cambio de soporte delantero, bomba de agua, correa accesorios, reten de cola cigüeñal, punta homocinetica y reparación del carter. Vehículo de alto valor en mantenciones correctivas. Se sugiere cambio o dar de baja.</t>
+          <t xml:space="preserve">Se realizo por el contrato de mantención vigente, cambio de soporte delantero, bomba de agua, correa accesorios, reten de cola cigüeñal, punta homocinetica y reparación del carter. Vehículo de alto valor en mantenciones correctivas. Se sugiere cambio o dar de baja. </t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G8" t="n">
-        <v>10245</v>
+        <v>28557</v>
       </c>
       <c r="H8" t="n">
         <v>875090</v>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">Nueva. </t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">Funcionando de forma optima. </t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
         <v>2018</v>
       </c>
       <c r="G9" t="n">
-        <v>244781</v>
+        <v>260900</v>
       </c>
       <c r="H9" t="n">
         <v>2261761</v>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Saturación de DPF (filtro de partículas) sistema de admisión saturado.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reparada, funcionando de forma optima  con recepcion conforme.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
         <v>2013</v>
       </c>
       <c r="G10" t="n">
-        <v>193017</v>
+        <v>211726</v>
       </c>
       <c r="H10" t="n">
         <v>875090</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Comodato RM</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Falla kit de embrague.</t>
+          <t>Falla kit de embrague. Falla alza vidrios delanteros, reparación de aire acondicionado.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Se realizo por el contratista el cambio del kit de embrague y rodamiento de empuje. Vehiculo transferido por SERVIU RM por tanto no contamos con informacion acumulada de gasto.</t>
+          <t xml:space="preserve">A la espera de ingreso a taller </t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
         <v>2013</v>
       </c>
       <c r="G11" t="n">
-        <v>21889</v>
+        <v>22062</v>
       </c>
       <c r="H11" t="n">
         <v>10835518</v>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reparación caja de cambio.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reparada, funcionando de forma optima  con recepcion conforme.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
         <v>2008</v>
       </c>
       <c r="G12" t="n">
-        <v>141348</v>
+        <v>142710</v>
       </c>
       <c r="H12" t="n">
         <v>4965482</v>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reparación sistema de freno.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reparada, funcionando de forma optima  con recepcion conforme.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
         <v>2013</v>
       </c>
       <c r="G13" t="n">
-        <v>148711</v>
+        <v>150300</v>
       </c>
       <c r="H13" t="n">
         <v>9759567</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t xml:space="preserve">inactivo </t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Falla freno - servo freno - bateria - rodamiento - eje muñon.</t>
+          <t>Falla freno - servo freno - batería - rodamiento - eje muñón, varillas selectoras de cambios.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Se realizo por el contratista cambio de bomba de freno, reparación de servo freno, cambio de bateria, kit de rodamiento y reparación del eje muñon.</t>
+          <t xml:space="preserve">A la espera de ingreso a taller </t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
         <v>2019</v>
       </c>
       <c r="G14" t="n">
-        <v>86454</v>
+        <v>94676</v>
       </c>
       <c r="H14" t="n">
         <v>2530050</v>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Falla en caja de cambio - eje piloto - rodamiento - retenes - sincronizador - discos - tambor trasero - masa delantera.</t>
+          <t>Falla en caja de cambio - Eje piloto - Rodamiento - Retenes - Sincronizador - Discos - Tambor trasero - Masa delantera, filtro de partículas DPF saturado.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Se realizó por el contratista reparación de la caja de cambio, eje piloto, sincronizador y se cambiaron rodamiento de masa delantera, pastillas (discos), retenes.</t>
+          <t>Reparada, funcionando de forma optima  con recepcion conforme.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
         <v>2016</v>
       </c>
       <c r="G15" t="n">
-        <v>110467</v>
+        <v>119711</v>
       </c>
       <c r="H15" t="n">
         <v>8539732</v>
@@ -1861,12 +1861,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Falla en porta filtros - empaquetaduras - filtros petroleros - kit embrague - volante bimaza - reten rodamiento.</t>
+          <t xml:space="preserve">Falla en porta filtros - empaquetaduras - filtros de petróleo - kit embrague - volante bimasa - reten de rodamiento, enfriador de aceite, sellos de agua, tensor de correa de accesorios.
+</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Se realizó por el contratista, el cambio porta filtros y filtros petroleros, reten rodamiento eje piloto, kit de embrague. Reparación de volante bimaza.</t>
+          <t xml:space="preserve">Vehículo en mal estado se adjunta informe técnico. Se realizó por el contratista, el cambio porta filtros y filtros petroleros, reten rodamiento eje piloto, kit de embrague. Reparación de volante bimaza
+</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -1933,7 +1935,7 @@
         <v>2025</v>
       </c>
       <c r="G16" t="n">
-        <v>3113</v>
+        <v>31925</v>
       </c>
       <c r="H16" t="n">
         <v>875090</v>
@@ -1958,12 +1960,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">Nuevo. </t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">Funcionando de forma optima. </t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2030,7 +2032,7 @@
         <v>2011</v>
       </c>
       <c r="G17" t="n">
-        <v>366182</v>
+        <v>376950</v>
       </c>
       <c r="H17" t="n">
         <v>3399631</v>
@@ -2050,17 +2052,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Falla distribución - Bomba de agua (correa)</t>
+          <t xml:space="preserve">Falla distribución - Bomba de agua (correa), problemas mecánicos de motor de motor descomprimido, humo azul, problemas de anillos. 
+</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Requiere reemplazar este mini bus, debido a que con sus mas de 300 mil kilómetros, presenta constantes fallas en su motor debido al desgaste por sus años de uso y alto kilometraje, entre otras fallas propias del uso de la unidad. Además de contar con restricción vehicular, que lo deja fuera de circulación al menos un día a la semana, entre mayo y septiembre.  </t>
+          <t xml:space="preserve">Vehículo en mal estado se adjunta informe técnico.
+</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -2071,7 +2075,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2085,7 +2089,7 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2124,17 +2128,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Camioneta 4x2</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2009</v>
       </c>
       <c r="G18" t="n">
-        <v>221553</v>
+        <v>224836</v>
       </c>
       <c r="H18" t="n">
-        <v>7637222</v>
+        <v>8172722</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2142,11 +2146,11 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2156,12 +2160,16 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Fallas varias por los años de uso</t>
+          <t>Frenos ABS no funcionan, la calefacción funciona en forma intermitente, asientos en mal estado, este año 2026 se realizo cambio de deposito de carburante por deterioro que produjo filtracion de combustible</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>El Vehículo adquirido hace más de 15 años, presenta muchas intervenciones  con elevados gastos asociados a mantenciones y reparaciones. El vehiculo presenta problemas tales como: (frenos ABS no funcionan, la calefacción funciona en forma intermitente, asientos en mal estado.Se requiere a la brevedad posible la reposición de vehiculo, dado que el vehiculo actualmente esta funcionando bien , pero el año de fabricación es 2009, lo cual no es recomendable su circulación a gran altura geografica sobre los 3000  m.s.n.m., como lo es a la zona de COLCHANE (zona limite con Bolivia) y pueblos del interior de la Región de Tarapacá, dado que por las condiciones de los accesos y caminos es necesario poder movilizar al personal y a la autoridad en vehiculos mas modernos y con tracción 4 x 4.</t>
+          <t>El El vehículo institucional, adquirido hace más de 16 años y correspondiente al año de fabricación 2009, ha superado ampliamente su vida útil operativa, evidenciando un progresivo deterioro mecánico y funcional que ha significado numerosas intervenciones, mantenciones correctivas y elevados costos de reparación para el servicio. Entre las principales deficiencias detectadas se encuentran la inoperatividad del sistema de frenos ABS, el funcionamiento intermitente de la calefacción, el desgaste significativo de los asientos y, recientemente, durante el año 2026, la necesidad de reemplazar el depósito de combustible debido a su avanzado deterioro, el cual provocó filtraciones que comprometían las condiciones de seguridad del vehículo.
+Desde una perspectiva técnica, la antigüedad del vehículo afecta directamente su confiabilidad mecánica, disponibilidad operativa y nivel de seguridad para enfrentar trayectos de alta exigencia. Los componentes estructurales, sistemas de suspensión, dirección, transmisión y frenado presentan un desgaste acumulativo propio de los años de uso, aumentando la probabilidad de fallas imprevistas, especialmente en zonas aisladas donde el acceso a servicios de asistencia mecánica es limitado o inexistente. Asimismo, el diseño y equipamiento de seguridad corresponden a estándares tecnológicos de hace más de una década, los cuales han sido ampliamente superados por las actuales exigencias en materia de seguridad vial y desempeño vehicular.
+Lo anterior adquiere especial relevancia considerando las características geográficas y operacionales de la Región de Tarapacá. Gran parte de las actividades institucionales requieren desplazamientos frecuentes hacia la comuna de Colchane, localidades fronterizas y diversos pueblos del interior, ubicados sobre los 3.000 metros sobre el nivel del mar, con recorridos que implican extensas distancias, pronunciadas pendientes, caminos de ripio, superficies irregulares y condiciones climáticas extremas. Estas características demandan vehículos con mayores prestaciones técnicas, robustez mecánica y capacidad de tracción.
+En este contexto, el vehículo actualmente utilizado no resulta el más adecuado para enfrentar de manera permanente este tipo de operaciones, especialmente considerando su año de fabricación y el desgaste acumulado de sus componentes. Técnicamente se recomienda disponer de una unidad más moderna, preferentemente equipada con tracción 4x4, control de estabilidad, sistemas avanzados de frenado y mejores condiciones de desempeño para circulación en altura geográfica. Este tipo de vehículos ofrece una mayor adherencia y estabilidad en caminos no pavimentados, mejor capacidad de respuesta en terrenos complejos y mayores niveles de seguridad para sus ocupantes.
+Por lo anterior, la reposición del vehículo institucional constituye una necesidad operativa debidamente justificada, orientada a garantizar la continuidad del servicio, resguardar la integridad física del personal y de la autoridad regional en comisiones de servicio, disminuir el riesgo de interrupciones por fallas mecánicas y optimizar el uso de los recursos públicos, evitando continuar destinando recursos crecientes a la mantención de un vehículo cuya vida útil se encuentra ampliamente excedida. La renovación permitirá contar con un medio de transporte acorde a las exigencias territoriales de la Región de Tarapacá y a los estándares de seguridad que demanda el cumplimiento de las funciones institucionales en zonas de difícil acceso y alta complejidad geográfica.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2236,7 +2244,7 @@
         <v>2018</v>
       </c>
       <c r="G19" t="n">
-        <v>74524</v>
+        <v>81318</v>
       </c>
       <c r="H19" t="n">
         <v>1293227</v>
@@ -2266,7 +2274,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Vehiculo a la fecha del presente informe, no presenta problemas.</t>
+          <t xml:space="preserve">Vehiculo a la fecha del presente informe, no presenta problemas </t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -2333,10 +2341,10 @@
         <v>2018</v>
       </c>
       <c r="G20" t="n">
-        <v>182705</v>
+        <v>194030</v>
       </c>
       <c r="H20" t="n">
-        <v>1199600</v>
+        <v>8141810</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2344,7 +2352,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2353,21 +2361,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Falla en los frenos
-Fallas en caja de cambio
-Fallas en sistema de ararnque</t>
+          <t>no aplica</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Falla en los frenos
-Fallas en caja de cambio
-Fallas en sistema de ararnque</t>
+          <t>Modelo de Vehiculo Station Wagon</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2388,7 +2392,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2397,7 +2401,7 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2438,18 +2442,40 @@
       <c r="F21" t="n">
         <v>2026</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>12668</v>
+      </c>
+      <c r="H21" t="n">
+        <v>399269</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Modelo de Vehiculo Station Wagon</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2516,10 +2542,10 @@
         <v>2018</v>
       </c>
       <c r="G22" t="n">
-        <v>169643</v>
+        <v>186362</v>
       </c>
       <c r="H22" t="n">
-        <v>3346356</v>
+        <v>3483206</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2527,7 +2553,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2546,7 +2572,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Vehículo no ha tenido fallas se considera como priorización media debido al año y kilometraje.</t>
+          <t>LA CLASIFICACIÓN MEDIA SE BASA EN LA ANTIGÜEDAD DEL VEHICULO Y SU KILOMETRAJE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -2606,17 +2632,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2024</v>
       </c>
       <c r="G23" t="n">
-        <v>20870</v>
+        <v>40303</v>
       </c>
       <c r="H23" t="n">
-        <v>276405</v>
+        <v>659606</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2706,10 +2732,10 @@
         <v>2026</v>
       </c>
       <c r="G24" t="n">
-        <v>3321</v>
+        <v>24425</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>836760</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2717,7 +2743,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2726,12 +2752,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>SIN FALLAS</t>
+          <t>Sin falla</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2747,7 +2773,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2761,7 +2787,7 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2803,10 +2829,10 @@
         <v>2024</v>
       </c>
       <c r="G25" t="n">
-        <v>20064</v>
+        <v>30952</v>
       </c>
       <c r="H25" t="n">
-        <v>189233</v>
+        <v>812109</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2814,7 +2840,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2823,12 +2849,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>SIN FALLAS</t>
+          <t>Desgaste pastillas de freno</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2844,7 +2870,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2858,7 +2884,7 @@
         </is>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2893,17 +2919,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMIONETA </t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>2026</v>
       </c>
       <c r="G26" t="n">
-        <v>4496</v>
+        <v>24162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>534025</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2911,7 +2937,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2923,7 +2949,11 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NINGUNA </t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -2984,17 +3014,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMIONETA </t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>2020</v>
       </c>
       <c r="G27" t="n">
-        <v>176581</v>
+        <v>201719</v>
       </c>
       <c r="H27" t="n">
-        <v>9689517</v>
+        <v>8777690</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3002,7 +3032,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3011,25 +3041,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>mecanico</t>
+          <t xml:space="preserve">hasta le momento ninguna </t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Durante el año 2025, el vehículo asignado ha requerido mantenciones de alto costo que han impactado significativamente el presupuesto operativo. Las intervenciones realizadas son las siguientes:
-10/02/2025: Cambio de termostato (Orden de trabajo N° 632-1-AG25).
-21/03/2025: Revisión y reparación por encendido de luz Check Engine, alarma y código de sensor de oxígeno, el cual bloqueaba el funcionamiento del vehículo (Orden de trabajo N° 632-8-AG25).
-25/09/2025: Reparación mayor (Orden de trabajo N° 632-34-AG25).
-Estas reparaciones evidencian el desgaste del vehículo y los altos costos asociados a su mantención, lo que afecta la continuidad operativa.
-Adicionalmente, se debe considerar que las camionetas en nuestra región están sometidas a condiciones extremas debido a la naturaleza del territorio:
-Traslados constantes en emergencias como incendios, lluvias y terrenos con barro.
-Gran parte de los desplazamientos se realizan en cerros, caminos no pavimentados y calles estrechas.
-Por estas razones, resulta indispensable contar con una camioneta de alta complejidad que garantice la seguridad de nuestros conductores y funcionarios, así como la eficiencia en la atención de las labores propias del servicio.</t>
+          <t xml:space="preserve">las reparaciones altas que se han realizado en la camioneta son : cambio de termostato , cambio de pastillas  sensor de oxigeno etc </t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -3040,7 +3062,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3054,7 +3076,7 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3089,17 +3111,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMIONETA </t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2024</v>
       </c>
       <c r="G28" t="n">
-        <v>53389</v>
+        <v>77166</v>
       </c>
       <c r="H28" t="n">
-        <v>1563130</v>
+        <v>3314905</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3119,7 +3141,11 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NINGUNA </t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3162,11 +3188,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PGC 2026-Subse-selico 228</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
         <v>28</v>
       </c>
@@ -3177,30 +3199,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GYXT42</t>
+          <t>VLJW60</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2015</v>
+        <v>2026</v>
       </c>
       <c r="G29" t="n">
-        <v>242541</v>
+        <v>13305</v>
       </c>
       <c r="H29" t="n">
-        <v>10305480</v>
+        <v>342258</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Petrolero</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3209,19 +3231,15 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Falla de freno, reiterados problemas como por ejemplo: sensor abs delantero, scaner, cambio perno de rueda y axial de direccion, cambio de pastilla de freno,rectificado de disco.</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Considerando 10 años de funcionamiento, los costos por mantenciones correctivas han provocado un alto costo por este servicio, equivalente a M$ 10.305. Su rendimiento por KM también ha disminuido.  Durante el ultimo tiempo ha presentado variables fallas no menores en  frenos,  sensor abs delantero, scaner, cambio perno de rueda y axial de direccion, cambio de pastilla de freno,rectificado de disco.</t>
-        </is>
-      </c>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>Es el vehículo más antiguo del servicio, alto gasto en mantención y alto kilometraje.</t>
@@ -3229,30 +3247,30 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3283,17 +3301,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2025</v>
       </c>
       <c r="G30" t="n">
-        <v>15138</v>
+        <v>29430</v>
       </c>
       <c r="H30" t="n">
-        <v>334127</v>
+        <v>896192</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3315,7 +3333,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>No Presenta Fallas de Funcionamiento</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3360,7 +3378,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PGC 2026-Subse-selico 228</t>
+        </is>
+      </c>
       <c r="B31" t="n">
         <v>30</v>
       </c>
@@ -3371,30 +3393,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VLJW60</t>
+          <t>GYXT42</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="G31" t="n">
-        <v>1061</v>
+        <v>246072</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>10554964</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -3403,42 +3425,46 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>No Presenta Fallas de Funcionamiento</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>Falla de freno, reiterados problemas como por ejemplo: sensor abs delantero, scaner, cambio perno de rueda y axial de direccion, cambio de pastilla de freno,rectificado de disco.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Considerando 11 años de funcionamiento, los costos por mantenciones correctivas han provocado un alto costo por este servicio, equivalente a M$ 10,554. Su Rendimiento por KM también ha disminuido.  Durante el ultimo tiempo ha presentado variables fallas no menores en  frenos,  sensor abs delantero, scaner, cambio perno de rueda y axial de direccion, cambio de pastilla de freno,rectificado de disco.</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3471,7 +3497,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -3481,7 +3507,7 @@
         <v>175508</v>
       </c>
       <c r="H32" t="n">
-        <v>4693455</v>
+        <v>4993752</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3489,7 +3515,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -3564,7 +3590,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -3582,7 +3608,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3601,7 +3627,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Único vehículo con caracteristicas de camioneta, fallas propias del desgaste de antigüedad y poco uso por condiciones poco recomendables en cuanto a confort de los pasajeros.</t>
+          <t xml:space="preserve"> La camioneta constituye el único vehículo de su tipo en la institución, siendo indispensable para el desarrollo de labores en terreno , ademas el  vehículo presenta fallas asociadas al desgaste natural producto de su antigüedad y  su uso se ha visto reducido considerablemente, ya que las condiciones de confort para los pasajeros no son las adecuadas.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3668,7 +3694,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -3678,7 +3704,7 @@
         <v>322421</v>
       </c>
       <c r="H34" t="n">
-        <v>15913810</v>
+        <v>17301210</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3686,7 +3712,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3700,12 +3726,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Kit de embriague defectuoso y presentó falla en sistema de turbo, además de alternador y sistema electrico</t>
+          <t>Kit de embriague defectuoso y presentó falla en sistema de turbo.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>En general está presentando diversas fallas por el avance del kilometraje, detectadas en ultimo diagnóstico realizado en diciembre 2025.</t>
+          <t>Considerando la antigüedad y el alto kilometraje acumulado del vehículo institucional, así como las diversas fallas mecánicas y operativas que ha presentado durante los últimos años, se estima necesario gestionar su reemplazo con el fin de asegurar la continuidad operacional del servicio y resguardar la seguridad de los funcionarios.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3770,17 +3796,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>2026</v>
       </c>
       <c r="G35" t="n">
-        <v>2418</v>
+        <v>20000</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>573200</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3788,7 +3814,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3861,25 +3887,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>2016</v>
       </c>
       <c r="G36" t="n">
-        <v>184490</v>
+        <v>200688</v>
       </c>
       <c r="H36" t="n">
-        <v>7352341.78</v>
+        <v>8304117</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3888,7 +3914,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3898,7 +3924,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CAMBIO DE CORREA AC - REPARACIÓN KIT DE EMBRAGUE - AJUSTE DE FRENOS Y REVISIÓN CALIPER - LIMPIEZA Y REGENERACION DPF, CAMBIO PASTILLAS DE FRENO Y REEMPLAZO AMPOLLETA DE CALEFACCIÓN - REEMPLAZO DE TAMBO Y PATINES DE FRENO</t>
+          <t>CAMBIO DE CORREA AC - REPARACIÓN KIT DE EMBRAGUE - AJUSTE DE FRENOS Y REVISIÓN CALIPER - LIMPIEZA Y REGENERACION DPF, CAMBIO PASTILLAS DE FRENO Y REEMPLAZO AMPOLLETA DE CALEFACCIÓN - REEMPLAZO DE TAMBO Y PATINES DE FRENO - AJUSTE FRENO AUXILIAR - BALANCEO</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -3909,7 +3935,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3923,11 +3949,11 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3960,25 +3986,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>2012</v>
       </c>
       <c r="G37" t="n">
-        <v>255889</v>
+        <v>269375</v>
       </c>
       <c r="H37" t="n">
-        <v>12890520.82</v>
+        <v>15205885</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3997,7 +4023,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>CAMBIO CORREA COMPRESOR, CARGA REFRIGERANTE - REVISIÓN Y REPARACIÓN AC - REPARACION DE CALIPERS, AMORTIGUADORES - REPARACIÓN DE ALTERNADOR - REPARACIÓN DE TREN DELANTERO Y TERMINALES DIRECCIÓN - CAMBIO CORREA COMPRESOR, CARGA REFRIGERANTE</t>
+          <t>CAMBIO CORREA COMPRESOR, CARGA REFRIGERANTE - REVISIÓN Y REPARACIÓN AC - REPARACION DE CALIPERS, AMORTIGUADORES - REPARACIÓN DE ALTERNADOR - REPARACIÓN DE TREN DELANTERO Y TERMINALES DIRECCIÓN - CAMBIO CORREA COMPRESOR, CARGA REFRIGERANTE- CAMBIO INTERCOOLER-RADIADOR INTERCOOLER - CAMBIO BIELETAS - CAMBIO BUJE BARRA ESTABILIZADORA - CAMBIO RELE COMPRESOR DE AIRE ACONDICIONADO - ESCANER MOTOR - CAMBIO MANILLA PUERTA INTERIOR - AJUSTE FRENOS - REAPRETE SOPORTES TREN DELANTERO - CAMBIO PATINES DE FRENO- CAMBIO PLUMILLAS - CAMBIO SOQUETES DE FOCO MAYOR - ASEO Y LUBRICACION DE CALIPER DE FRENOS</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4061,7 +4087,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DHFZ38</t>
+          <t>DFHZ38</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4073,10 +4099,10 @@
         <v>2011</v>
       </c>
       <c r="G38" t="n">
-        <v>283000</v>
+        <v>290569</v>
       </c>
       <c r="H38" t="n">
-        <v>15999577.23</v>
+        <v>19829598</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4084,7 +4110,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4103,7 +4129,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>REPARACION DE RECOLECTOR DE ESCAPE Y CATALITICO - REPARACIÓN PUERTA DELANTERA - CAMBIO BIELETAS Y JUEGO DE PASTILLA DE FRENOS - CAMBIO DE BATERIA</t>
+          <t>REPARACION DE RECOLECTOR DE ESCAPE Y CATALITICO - REPARACIÓN PUERTA DELANTERA - CAMBIO BIELETAS Y JUEGO DE PASTILLA DE FRENOS - CAMBIO DE BATERIA - CAMBIO CATALIZADOR SECUNDARIO - EMPAQUETADURA UNION CATALIZADOR - SUMINISTRO Y CAMBIO DE BUJIA DE ENCENDIDO - DISINFECTANTE AIRE ACONDICIONADO - REPARACION ALZAVIDRIO - BALANCEO - AJUSTE FRENO AUXILIAR - CAMBIO PLUMILLAS - FILTRO COMBUSTIBLE - CAMBIO PATINES DE FRENOS - ASEO LUBRICACION CALIPER DE FRENOS - CAMBIO REFRIGERANTE - DESMONTAJE Y MONTAJE DE CULATA - CAMBIO EMPAQUETADURA - JUEGO ANILLOS PISTON - CAMBIO JUEGOS DE ANILLOS BRUÑIDO CILINDRO - CAMBIO VALVULAS Y RETENES DE VALVULAS CULATA.</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4168,21 +4194,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>2025</v>
       </c>
       <c r="G39" t="n">
-        <v>11282</v>
+        <v>27156</v>
       </c>
       <c r="H39" t="n">
         <v>311195</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -4198,10 +4224,14 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>presenta fallas diversas por alto kilometraje</t>
+          <t>Mantención preventiva</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -4268,10 +4298,10 @@
         <v>2026</v>
       </c>
       <c r="G40" t="n">
-        <v>2678</v>
+        <v>20658</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1077200</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4279,7 +4309,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -4291,10 +4321,14 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>presenta fallas diversas por alto kilometraje</t>
+          <t>Mantenciones facturadas hasta lon 50.000 km</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
@@ -4354,27 +4388,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>2024</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>50216</v>
+      </c>
+      <c r="H41" t="n">
+        <v>917901</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>11</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Región no envia informacion respecto de las mantenciones, solicitado en diciembre 2025 (se mantiene informacion enviada por Victor S.)</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4433,27 +4477,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>2026</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>24035</v>
+      </c>
+      <c r="H42" t="n">
+        <v>899999</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Región no envia informacion respecto de las mantenciones, solicitado en diciembre 2025 (se mantiene informacion enviada por Victor S.)</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4799,17 +4853,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>2019</v>
       </c>
       <c r="G46" t="n">
-        <v>162284</v>
+        <v>180000</v>
       </c>
       <c r="H46" t="n">
-        <v>1909171</v>
+        <v>1304880</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4817,7 +4871,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4831,12 +4885,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Sistema de Frenos</t>
+          <t>Falla en el sistema de doble tracción (4x4), específicamente en el sensor asociado a la activación y funcionamiento de la tracción baja (4L) de la camioneta Toyota.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Ha requerido un mayor gasto en mantención, debido a la necesidad de realizar mantención del sistema DPF (Filtro de Partículas Diésel) y reparación/mantención del sistema de frenos.</t>
+          <t>Se ha identificado una falla en el sistema de doble tracción del vehículo institucional, asociada al sensor de tracción baja, lo que podría afectar el correcto funcionamiento y la activación del sistema 4x4. Esta situación requiere una evaluación técnica especializada para determinar el origen de la falla y efectuar el reemplazo del componente defectuoso, en caso de corresponder. Considerando las condiciones geográficas y climáticas de la Región de Aysén, así como la necesidad de realizar desplazamientos institucionales por caminos rurales, de ripio y en condiciones de nieve o hielo, resulta fundamental mantener el sistema de doble tracción en óptimas condiciones para resguardar la seguridad de los funcionarios y garantizar la continuidad operativa del vehículo. Se solicita gestionar la revisión técnica y cotización correspondiente para su reparación.</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4901,17 +4955,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>2026</v>
       </c>
       <c r="G47" t="n">
-        <v>1386</v>
+        <v>14000</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>229001</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4919,7 +4973,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4994,15 +5048,13 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>2026</v>
       </c>
-      <c r="G48" t="n">
-        <v>113</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>0</v>
       </c>
@@ -5011,7 +5063,9 @@
           <t>Bencinero</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>10</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5087,17 +5141,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>2020</v>
       </c>
-      <c r="G49" t="n">
-        <v>93421</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>318346</v>
+        <v>1892305</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5105,7 +5157,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5185,10 +5237,10 @@
         <v>2015</v>
       </c>
       <c r="G50" t="n">
-        <v>97000</v>
+        <v>105293</v>
       </c>
       <c r="H50" t="n">
-        <v>4788375</v>
+        <v>6406358</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5210,14 +5262,10 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frenos, discos, embriague, </t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Antigüedad vehiculo 10 años, falla en el sistema de frenos, desgaste en general.                                                                                                 Se esta tramitando la compra de un diagnostico general del vehiculo esto no ha podido ser realizado debido al bajo presupuesto que nos designan, actualmente esta camioneta esta presentado problemas en el embriague, direccion, alineacion, balance, luces principales, no encienden las luces del tablero y otros.</t>
-        </is>
-      </c>
+          <t>Cambio Sistema kit de Embrague, Alineacion y balanceo, Panel de luces tablero, falla en los discos y desgaste en general</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">Es el vehículo más antiguo del servicio.
@@ -5236,20 +5284,20 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5289,10 +5337,10 @@
         <v>2019</v>
       </c>
       <c r="G51" t="n">
-        <v>54206</v>
+        <v>61947</v>
       </c>
       <c r="H51" t="n">
-        <v>1591205</v>
+        <v>2935322</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5314,12 +5362,13 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Frenos</t>
+          <t>Freno y cambio de neumáticos</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Falla sistema de freno y desgaste por uso, aumentando la probabilidad de general un accidente a los funcionarios</t>
+          <t xml:space="preserve"> Falla de sistema de frenos por desgaste de pastillas lo cual aumenta la probabilidad de algún siniestro.
+Cambio de neumáticos por desgaste, lo que  aumenta que pueda derrapar y causar un accidente.</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
@@ -5379,24 +5428,46 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>2026</v>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>4022</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>13</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ninguna</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>vehiculo nuevo</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5454,17 +5525,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>2025</v>
       </c>
       <c r="G53" t="n">
-        <v>5636</v>
+        <v>24113</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>761864</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5472,7 +5543,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5486,14 +5557,10 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Vehiculo nuevo,  sin problemas</t>
-        </is>
-      </c>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5553,17 +5620,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>2019</v>
       </c>
       <c r="G54" t="n">
-        <v>171972</v>
+        <v>197694</v>
       </c>
       <c r="H54" t="n">
-        <v>5389989</v>
+        <v>7026362</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5571,7 +5638,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -5580,19 +5647,15 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>sin observaciones</t>
-        </is>
-      </c>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5654,17 +5717,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>2016</v>
       </c>
       <c r="G55" t="n">
-        <v>227963</v>
+        <v>232360</v>
       </c>
       <c r="H55" t="n">
-        <v>11328991</v>
+        <v>12332991</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5672,11 +5735,11 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5686,12 +5749,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Mecánica y electrónica:  motor,  sistema de frenos y suspensión</t>
+          <t>Mecanica</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Cumple su vida util de 9 años en el año 2025, considerar que el año 2022,  producto de un siniestro ocurrido el año 2021,  se tuvo que reparar una pieza denominada carter y precarter,  el cual no estaba en Chile ni en el extranjero,  la pieza se pudo reparar y actualmente el vehículo transita en buenas condiciones pero es importante relevar,  esta repararción. En el año 2023 ya presentó una nueva falla producto del siniestro,  en el radiador,  lo cual obligó a tener el vehículo sin poder utilizar por un buen tiempo. Vamos a seguir realizando mantenciones preventivas . Se solicitaría por cambio de vehículo de las similares características capacidad y tipo de combustible (petroleo) y de una marca confiable y para 7 pasajeros.  Además indicar que este pasado año 2024,  se realizó una mantención con cambio de disco y prensa de volante dinámico que ascendió a un valor de $2,085,000.-  Hay que hacerle cambio de amortiguadores,  disco y pastillas de freno,  tiene ruido de motor que podría significar una pana de alto costo y tiempo que no se pueda utilizar,  revisión de sistema de inyección,  cuando parte humea un poco - al partir motor disparejo.  Esto es sólo al partir el vehículo.</t>
+          <t>Este vehículo pronto pasará a proceso administrativo de baja,  estamos a la espera que llegue el otro vehículo que solicitamos y se autorizó,  un Hyundai Tucson.  Vehiculo llegaría a mediados de octubre +/-</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -6000,17 +6063,31 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Station wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>2019</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>163102</v>
+      </c>
+      <c r="H59" t="n">
+        <v>819000</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>No indica</t>
@@ -6018,7 +6095,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Región no envia informacion respecto de las mantenciones, solicitado en diciembre 2025 (se mantiene informacion enviada por Victor S.)</t>
+          <t>Problemas de arranque</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6040,11 +6117,11 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -6081,27 +6158,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Station wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>2019</v>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>199017</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1041100</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>No indica</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Región no envia informacion respecto de las mantenciones, solicitado en diciembre 2025 (se mantiene informacion enviada por Victor S.)</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -6121,11 +6208,11 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -7087,17 +7174,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CAMION</t>
+          <t>Camioneta</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>2013</v>
       </c>
       <c r="G71" t="n">
-        <v>46015</v>
+        <v>47955</v>
       </c>
       <c r="H71" t="n">
-        <v>5139981</v>
+        <v>5959058</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7119,24 +7206,15 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Sin aire acondicionado .
-Latas oxidadas en carrocería.
-Vehículo presta servicios de carga de logista en  actividades de entregas de viviendas y otros.
-Por seguridad para los  conductores ,funcionarios y funcionarias  se solicita la renovación.</t>
+          <t>VIDA UTIL 13 AÑOS</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>No tiene mucho movimiento por lo que este año no se le ha realizado mantención.
-Las distancias  de recorrido entre comunas  de la región son   aproximadamente  de 550  y  650 kilómetros  de  ida y vuelta hasta el Serviu de  Antofagasta.</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Vehículo con más de 8 años de antigüedad, alto gasto en mantención acumulado, gran utilidad para cubrir las necesidades de traslado de carga para los eventos del servicio; sillas, parlantes, pódium, papelería, etc, los cuales quedan a grandes distancias y un clima hostil.
-Rodrigo Villaroel mediante correo de fecha 09 de abril 2026, solicita la renovacion, ya que presenta avanzado estado de oxidación en el techo, con agujeros en la zona de carga, aire acondicionado en mal estado.</t>
-        </is>
-      </c>
+          <t>Renovación de vehículo esta  en proceso de compra en licitación, octubre 2026</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -7193,17 +7271,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MINIBUS</t>
+          <t>Station Wagon</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G72" t="n">
-        <v>68848</v>
+        <v>68912</v>
       </c>
       <c r="H72" t="n">
-        <v>3113185</v>
+        <v>5588385</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7220,7 +7298,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7244,12 +7322,12 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -7293,7 +7371,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>Station Wagon</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -7382,7 +7460,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>Station Wagon</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -7475,7 +7553,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>Station Wagon</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -7568,17 +7646,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>2026</v>
       </c>
       <c r="G76" t="n">
-        <v>1347</v>
+        <v>26487</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>987210</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -7664,10 +7742,10 @@
         <v>2025</v>
       </c>
       <c r="G77" t="n">
-        <v>18077</v>
+        <v>31417</v>
       </c>
       <c r="H77" t="n">
-        <v>290907</v>
+        <v>1050101</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -7746,17 +7824,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>2020</v>
       </c>
       <c r="G78" t="n">
-        <v>135928</v>
+        <v>157352</v>
       </c>
       <c r="H78" t="n">
-        <v>5919690</v>
+        <v>7323890</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7830,22 +7908,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KBLS52</t>
+          <t>KBLS50</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>2018</v>
       </c>
       <c r="G79" t="n">
-        <v>396741</v>
+        <v>431259</v>
       </c>
       <c r="H79" t="n">
-        <v>11790925</v>
+        <v>14954016</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7857,7 +7935,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7871,11 +7949,7 @@
           <t xml:space="preserve">El año 2026 el vehículo tendra una antigüedad de 8  años , el cual cuenta con uso permanete,  diariamente con motivos de inspecciones de obras recorre comunas de  toda la región de Atacama , vehiculo  ha recorrido 75.975  kilometros el año 2025. </t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Vehículo con mas de 8 años de antigüedad, alto kilometraje y alto gasto en mantención acumulado.</t>
-        </is>
-      </c>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -7936,17 +8010,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>2017</v>
       </c>
       <c r="G80" t="n">
-        <v>307827</v>
+        <v>339105</v>
       </c>
       <c r="H80" t="n">
-        <v>10574973</v>
+        <v>12480530</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7972,11 +8046,7 @@
           <t xml:space="preserve">El año 2026 el vehículo tendra una antigüedad de 9  años , el cual cuenta con uso permanete,  diariamente con motivos de inspecciones de obras recorre comunas de  toda la región de Atacama , vehiculo  ha recorrido 65.599  kilometros el año 2025. </t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Es el vehículo más antiguo del servicio, alto gasto en mantención y alto kilometraje.</t>
-        </is>
-      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -8043,10 +8113,20 @@
       <c r="F81" t="n">
         <v>2026</v>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>300</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>16</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -8058,7 +8138,11 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Por antigüedad no corresponde recambio</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8123,10 +8207,10 @@
         <v>2019</v>
       </c>
       <c r="G82" t="n">
-        <v>160250</v>
+        <v>181041</v>
       </c>
       <c r="H82" t="n">
-        <v>6735690</v>
+        <v>7635690</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -8216,10 +8300,10 @@
         <v>2020</v>
       </c>
       <c r="G83" t="n">
-        <v>111799</v>
+        <v>130509</v>
       </c>
       <c r="H83" t="n">
-        <v>4395650</v>
+        <v>5395650</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8258,7 +8342,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -8267,7 +8351,7 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -8309,10 +8393,10 @@
         <v>2020</v>
       </c>
       <c r="G84" t="n">
-        <v>187212</v>
+        <v>204869</v>
       </c>
       <c r="H84" t="n">
-        <v>9500680</v>
+        <v>10350598</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8402,10 +8486,10 @@
         <v>2023</v>
       </c>
       <c r="G85" t="n">
-        <v>73437</v>
+        <v>204869</v>
       </c>
       <c r="H85" t="n">
-        <v>2773883</v>
+        <v>10350598</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8444,16 +8528,16 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -8495,10 +8579,10 @@
         <v>2024</v>
       </c>
       <c r="G86" t="n">
-        <v>48793</v>
+        <v>59838</v>
       </c>
       <c r="H86" t="n">
-        <v>1438000</v>
+        <v>2538000</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8588,10 +8672,10 @@
         <v>2025</v>
       </c>
       <c r="G87" t="n">
-        <v>27473</v>
+        <v>56593</v>
       </c>
       <c r="H87" t="n">
-        <v>733353</v>
+        <v>1683000</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8681,10 +8765,10 @@
         <v>2025</v>
       </c>
       <c r="G88" t="n">
-        <v>18765</v>
+        <v>40483</v>
       </c>
       <c r="H88" t="n">
-        <v>530000</v>
+        <v>1800569</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8771,7 +8855,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MINIBUS</t>
+          <t>Minibus</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -8852,7 +8936,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PGC2026-pendiente</t>
+        </is>
+      </c>
       <c r="B90" t="n">
         <v>89</v>
       </c>
@@ -8863,22 +8951,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LBXY81</t>
+          <t>KBPC36</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G90" t="n">
-        <v>261904</v>
+        <v>235338</v>
       </c>
       <c r="H90" t="n">
-        <v>13693018</v>
+        <v>11448848</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8895,11 +8983,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Desgaste por kilometraje</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Vehículo con 8 años de antigüedad y más de 235 mil km. El kilometraje acumulado hace recomendable planificar su renovación, considerando el desgaste progresivo de componentes y el aumento esperado de los costos de mantenimiento.</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -8908,7 +9004,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8922,11 +9018,11 @@
         </is>
       </c>
       <c r="T90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8952,30 +9048,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VGJH19</t>
+          <t>LBXY81</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="G91" t="n">
-        <v>45213</v>
+        <v>261904</v>
       </c>
       <c r="H91" t="n">
-        <v>1160251</v>
+        <v>13693018</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Petrolero</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -8984,7 +9080,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -8992,7 +9088,7 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -9002,16 +9098,16 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -9030,9 +9126,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>2031</v>
-      </c>
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
         <v>91</v>
       </c>
@@ -9043,22 +9137,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LVDS61</t>
+          <t>SYVW13</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G92" t="n">
-        <v>210756</v>
+        <v>105736</v>
       </c>
       <c r="H92" t="n">
-        <v>27071968</v>
+        <v>3322045</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -9066,7 +9160,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -9075,7 +9169,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -9093,16 +9187,16 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
+          <t>no cumple</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
           <t>si cumple</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>si cumple</t>
-        </is>
-      </c>
       <c r="T92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -9121,11 +9215,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>PGC2026-pendiente</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
         <v>92</v>
       </c>
@@ -9136,22 +9226,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KBPC36</t>
+          <t>TFDP48</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="G93" t="n">
-        <v>235338</v>
+        <v>80096</v>
       </c>
       <c r="H93" t="n">
-        <v>11448848</v>
+        <v>2772881</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -9168,46 +9258,38 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Desgaste por kilometraje</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>Vehículo con 8 años de antigüedad y más de 235 mil km. El kilometraje acumulado hace recomendable planificar su renovación, considerando el desgaste progresivo de componentes y el aumento esperado de los costos de mantenimiento.</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9222,7 +9304,9 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="n">
+        <v>2031</v>
+      </c>
       <c r="B94" t="n">
         <v>93</v>
       </c>
@@ -9233,22 +9317,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SYVW13</t>
+          <t>LVDS61</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Camioneta 4x2</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="G94" t="n">
-        <v>105736</v>
+        <v>210756</v>
       </c>
       <c r="H94" t="n">
-        <v>3322045</v>
+        <v>27071968</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -9256,7 +9340,7 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -9265,7 +9349,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -9283,7 +9367,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -9292,7 +9376,7 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -9322,30 +9406,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TFDP48</t>
+          <t>VGJH19</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G95" t="n">
-        <v>80096</v>
+        <v>45213</v>
       </c>
       <c r="H95" t="n">
-        <v>2772881</v>
+        <v>1160251</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -9416,7 +9500,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -9505,7 +9589,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -9690,10 +9774,10 @@
         <v>2024</v>
       </c>
       <c r="G99" t="n">
-        <v>57086</v>
+        <v>67106</v>
       </c>
       <c r="H99" t="n">
-        <v>1173000</v>
+        <v>1740000</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -9779,10 +9863,10 @@
         <v>2024</v>
       </c>
       <c r="G100" t="n">
-        <v>67599</v>
+        <v>80266</v>
       </c>
       <c r="H100" t="n">
-        <v>1528000</v>
+        <v>2499338</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -9868,10 +9952,10 @@
         <v>2025</v>
       </c>
       <c r="G101" t="n">
-        <v>10438</v>
+        <v>28399</v>
       </c>
       <c r="H101" t="n">
-        <v>311793</v>
+        <v>1251211</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -9934,11 +10018,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>PGC 2026-Serviu-en proceso de compra</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
         <v>101</v>
       </c>
@@ -9949,7 +10029,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FKGK55</t>
+          <t>LZGC74</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9958,13 +10038,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="G102" t="n">
-        <v>306271</v>
+        <v>139081</v>
       </c>
       <c r="H102" t="n">
-        <v>14334928</v>
+        <v>4438863</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -9972,7 +10052,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -9981,51 +10061,38 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fallas electricas </t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>fallas electricas y antigüedad.</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Es el vehículo más antiguo, mayor gasto en mantención y alto kilometraje.
-Fallas varias debido a los años de uso, como por ejemplo el sistema eléctrico.</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
+          <t>no cumple</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
           <t>si cumple</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>si cumple</t>
-        </is>
-      </c>
       <c r="T102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -10051,22 +10118,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LZGC74</t>
+          <t>VPDD24</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>MINIBUS</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="G103" t="n">
-        <v>133517</v>
+        <v>4652</v>
       </c>
       <c r="H103" t="n">
-        <v>3471569</v>
+        <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -10074,7 +10141,7 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -10106,11 +10173,11 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -10129,11 +10196,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>PGC 2026-Serviu-en proceso de compra</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
         <v>103</v>
       </c>
@@ -10144,30 +10207,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>HHRW12</t>
+          <t>VPTP81</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>STATION WAGON</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2016</v>
+        <v>2026</v>
       </c>
       <c r="G104" t="n">
-        <v>163484</v>
+        <v>12473</v>
       </c>
       <c r="H104" t="n">
-        <v>4028822</v>
+        <v>530924</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Petrolero</t>
+          <t>Híbrido</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -10176,23 +10239,15 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 años de antigüedad </t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">solo por años de antigüedad  </t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -10207,11 +10262,11 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -10230,7 +10285,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
       <c r="B105" t="n">
         <v>104</v>
       </c>
@@ -10241,34 +10300,34 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VPDD24</t>
+          <t>WCXX86</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MINIBUS</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G105" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Petrolero</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10319,7 +10378,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
       <c r="B106" t="n">
         <v>105</v>
       </c>
@@ -10330,34 +10393,34 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VPTP81</t>
+          <t>WCXK88</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G106" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Híbrido</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -10424,17 +10487,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camioneta </t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>2019</v>
       </c>
       <c r="G107" t="n">
-        <v>222819</v>
+        <v>244815</v>
       </c>
       <c r="H107" t="n">
-        <v>12051252</v>
+        <v>9068144</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -10451,19 +10514,11 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>Sistema de Frenos</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>El vehículo mantiene un buen desempeño general y su historial muestra únicamente intervenciones asociadas al sistema de frenos y reemplazo de baterías, propias del desgaste por uso. No obstante, considerando que el vehículo cumple seis años de operación, se aproxima al periodo en que suelen manifestarse fallas de mayor costo vinculadas al desgaste de componentes mecánicos y electrónicos, como suspensión, embrague, sistema de inyección y sistemas auxiliares,  lo que incrementa el riesgo de detenciones no programadas y mayores gastos de mantención.</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -10521,17 +10576,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camioneta </t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F108" t="n">
         <v>2023</v>
       </c>
       <c r="G108" t="n">
-        <v>79943</v>
+        <v>80291</v>
       </c>
       <c r="H108" t="n">
-        <v>2985664</v>
+        <v>3196619</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -10610,17 +10665,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F109" t="n">
         <v>2024</v>
       </c>
       <c r="G109" t="n">
-        <v>58823</v>
+        <v>73079</v>
       </c>
       <c r="H109" t="n">
-        <v>1407207</v>
+        <v>2161694</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -10699,17 +10754,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F110" t="n">
         <v>2024</v>
       </c>
       <c r="G110" t="n">
-        <v>59385</v>
+        <v>81361</v>
       </c>
       <c r="H110" t="n">
-        <v>1801675</v>
+        <v>2609239</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -10788,17 +10843,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camioneta </t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>2025</v>
       </c>
       <c r="G111" t="n">
-        <v>29917</v>
+        <v>56914</v>
       </c>
       <c r="H111" t="n">
-        <v>933230</v>
+        <v>2195667</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -10877,17 +10932,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camioneta </t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G112" t="n">
-        <v>21893</v>
+        <v>36890</v>
       </c>
       <c r="H112" t="n">
-        <v>624074</v>
+        <v>902486</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10966,17 +11021,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>2025</v>
       </c>
       <c r="G113" t="n">
-        <v>8595</v>
+        <v>23156</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1407928</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -11055,17 +11110,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>2026</v>
       </c>
       <c r="G114" t="n">
-        <v>143</v>
+        <v>13547</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>354208</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -11151,10 +11206,10 @@
         <v>2024</v>
       </c>
       <c r="G115" t="n">
-        <v>49967</v>
+        <v>67017</v>
       </c>
       <c r="H115" t="n">
-        <v>2520357</v>
+        <v>3246204</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -11166,16 +11221,24 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siniestro perdida  total </t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Se requiere la renovación del vehículo fiscal debido a que la unidad actualmente asignada a la institución sufrió un siniestro de tránsito, determinándose su pérdida total, condición que imposibilita su restitución a la operación institucional.</t>
+        </is>
+      </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -11184,7 +11247,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -11198,7 +11261,7 @@
         </is>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -11240,10 +11303,10 @@
         <v>2024</v>
       </c>
       <c r="G116" t="n">
-        <v>85776</v>
+        <v>118247</v>
       </c>
       <c r="H116" t="n">
-        <v>4132970</v>
+        <v>5967506</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -11278,16 +11341,16 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -11332,10 +11395,20 @@
       <c r="F117" t="n">
         <v>2026</v>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>11914</v>
+      </c>
+      <c r="H117" t="n">
+        <v>279901</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>10</v>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -11412,10 +11485,10 @@
         <v>2018</v>
       </c>
       <c r="G118" t="n">
-        <v>250762</v>
+        <v>267848</v>
       </c>
       <c r="H118" t="n">
-        <v>19600312</v>
+        <v>22644818</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -11438,7 +11511,12 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Vehículo con 8 años de uso, el cual requerirá mantenciones e intervenciones correctivas mayores debido al kilometraje acumulado, presenta  desgaste asociado al alto kilometraje en  Motor Suspensión, frenos, embrague, transmisión, bomba de agua, correas y mangueras suelen necesitar reemplazo.</t>
+          <t>Vehículo con 8 años de uso y un elevado kilometraje acumulado, que presenta un nivel de desgaste que requiere intervenciones correctivas de carácter mayor.
+En el sistema de motor, presenta fuga y consumo de aceite, además de pérdida de compresión, situación que evidencia desgaste interno y hace necesario efectuar un diagnóstico y eventual ajuste de motor, incluyendo el reemplazo de los componentes que se encuentren deteriorados.
+Asimismo, presenta fallas asociadas al sistema DPF (filtro de partículas diésel), las cuales requieren diagnóstico, reparación y/o reemplazo de componentes, debido a su incidencia directa en el funcionamiento y rendimiento del motor.
+En cuanto al sistema de suspensión, se evidencian condiciones de desgaste que requieren intervención y reemplazo de componentes, con el objeto de mantener condiciones adecuadas de seguridad y estabilidad durante la conducción.
+Adicionalmente, presenta deficiencias en el sistema de tracción 4x4, por lo que se requiere efectuar una revisión y reparación de sus componentes, considerando que esta función resulta relevante para la operación del vehículo en caminos de difícil acceso y condiciones de terreno adversas.
+En consideración a lo anterior, el vehículo requiere una intervención mecánica de carácter mayor, cuyos costos de reparación y mantención deben ser evaluados en relación con su antigüedad, kilometraje acumulado, estado general y vida útil remanente.</t>
         </is>
       </c>
       <c r="O118" t="inlineStr"/>
@@ -11505,10 +11583,10 @@
         <v>2024</v>
       </c>
       <c r="G119" t="n">
-        <v>57497</v>
+        <v>87357</v>
       </c>
       <c r="H119" t="n">
-        <v>4174506</v>
+        <v>6664435</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -11543,7 +11621,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -11552,7 +11630,7 @@
         </is>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -11594,10 +11672,10 @@
         <v>2024</v>
       </c>
       <c r="G120" t="n">
-        <v>34460</v>
+        <v>103407</v>
       </c>
       <c r="H120" t="n">
-        <v>4346843</v>
+        <v>7292252</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -11632,16 +11710,16 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -11683,10 +11761,10 @@
         <v>2023</v>
       </c>
       <c r="G121" t="n">
-        <v>69054</v>
+        <v>84270</v>
       </c>
       <c r="H121" t="n">
-        <v>2711030</v>
+        <v>3445042</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -11772,10 +11850,10 @@
         <v>2020</v>
       </c>
       <c r="G122" t="n">
-        <v>153135</v>
+        <v>165083</v>
       </c>
       <c r="H122" t="n">
-        <v>7756013</v>
+        <v>11614541</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -11861,10 +11939,10 @@
         <v>2025</v>
       </c>
       <c r="G123" t="n">
-        <v>29427</v>
+        <v>45699</v>
       </c>
       <c r="H123" t="n">
-        <v>1386173</v>
+        <v>2167352</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -11950,10 +12028,10 @@
         <v>2025</v>
       </c>
       <c r="G124" t="n">
-        <v>15531</v>
+        <v>44692</v>
       </c>
       <c r="H124" t="n">
-        <v>894615</v>
+        <v>1717068</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -12039,10 +12117,10 @@
         <v>2025</v>
       </c>
       <c r="G125" t="n">
-        <v>5910</v>
+        <v>25421</v>
       </c>
       <c r="H125" t="n">
-        <v>402122</v>
+        <v>1266459</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -12128,10 +12206,10 @@
         <v>2026</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>22054</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>679801</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -12212,17 +12290,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F127" t="n">
         <v>2013</v>
       </c>
       <c r="G127" t="n">
-        <v>260902</v>
+        <v>267351</v>
       </c>
       <c r="H127" t="n">
-        <v>5981080</v>
+        <v>7848428</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -12230,7 +12308,7 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -12242,14 +12320,10 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vida útil </t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Desgaste por años de uso y vida útil alcanzada. La priorización corresponde a la necesidad de renovación por el año de adquisición  (2013), por tener prestaciones de menor confort, para caminos en mal estado en la región, es el vehículo que menor KM promedio tiene, lo que implica menor mantención por KM recorridos. Vehículo operativo.</t>
+          <t>Vida útil alcanzada  - problema en caja de cambio</t>
         </is>
       </c>
       <c r="O127" t="inlineStr"/>
@@ -12293,8 +12367,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
-        <v>2027</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PGC 2026-Serviu-en proceso de compra</t>
+        </is>
       </c>
       <c r="B128" t="n">
         <v>127</v>
@@ -12306,34 +12382,34 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>HHRW20</t>
+          <t>FKCW50</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="G128" t="n">
-        <v>262425</v>
+        <v>458393</v>
       </c>
       <c r="H128" t="n">
-        <v>25167251</v>
+        <v>20586251</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Petrolero</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -12341,22 +12417,13 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Falla odómetro, tablero. </t>
-        </is>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se repara en agosto 2025 por problemas de reten,  reparacion de arranque, kit de embrague entre otros, pero a Noviembre sigue presentando problemas en frenos y tablero. </t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>Vehículo con mas de 8 años de antigüedad, alto kilometraje y alto gasto en mantención acumulado.
-Presenta fallas en el sistema de arranque, enbrague y sistema de frenos.</t>
-        </is>
-      </c>
+          <t>Renovación en proceso de compra 2026</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -12412,34 +12479,34 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>FKCW50</t>
+          <t>HHRW20</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="G129" t="n">
-        <v>444176</v>
+        <v>272539</v>
       </c>
       <c r="H129" t="n">
-        <v>20112631</v>
+        <v>25802181</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -12447,22 +12514,13 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>Problema de Frenos</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">En Octubre 2025, se realiza cambio de juego de pastillas, freno delantero, bieletas de direccion, empaquetadura, cremalleras, axiales, kit reparación caliper, bateria. </t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>Es el más antiguo y con mayor gasto en mantención. (a pesar que tiene prioridad media)
-Fallas varias debido a los años de uso.</t>
-        </is>
-      </c>
+          <t>Renovación en proceso de compra 2026</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -12519,17 +12577,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F130" t="n">
         <v>2020</v>
       </c>
       <c r="G130" t="n">
-        <v>146402</v>
+        <v>170426</v>
       </c>
       <c r="H130" t="n">
-        <v>2617784</v>
+        <v>3042614</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -12537,7 +12595,7 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -12546,11 +12604,19 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Posible ajuste de motor </t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por ruptura de mangera del sistema de refrigueración, el vehiculo presento un sobrecalentamiento del motor, se encuentra en taller desde 08 septiembre 2026, esperando informe de taller. </t>
+        </is>
+      </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -12559,7 +12625,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -12573,7 +12639,7 @@
         </is>
       </c>
       <c r="T130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -12608,17 +12674,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F131" t="n">
         <v>2024</v>
       </c>
       <c r="G131" t="n">
-        <v>90837</v>
+        <v>11870</v>
       </c>
       <c r="H131" t="n">
-        <v>4753128</v>
+        <v>6328598</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -12626,7 +12692,7 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -12653,7 +12719,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -12662,7 +12728,7 @@
         </is>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -12697,17 +12763,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F132" t="n">
         <v>2024</v>
       </c>
       <c r="G132" t="n">
-        <v>69369</v>
+        <v>91481</v>
       </c>
       <c r="H132" t="n">
-        <v>2477834</v>
+        <v>3602523</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -12715,7 +12781,7 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -12781,22 +12847,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TWTL29</t>
+          <t>TRPP48</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F133" t="n">
         <v>2025</v>
       </c>
       <c r="G133" t="n">
-        <v>27549</v>
+        <v>32968</v>
       </c>
       <c r="H133" t="n">
-        <v>1079918</v>
+        <v>1492840</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -12804,7 +12870,7 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -12870,22 +12936,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TRPP48</t>
+          <t>TWTL29</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F134" t="n">
         <v>2025</v>
       </c>
       <c r="G134" t="n">
-        <v>12285</v>
+        <v>52649</v>
       </c>
       <c r="H134" t="n">
-        <v>390964</v>
+        <v>2106552</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -12893,7 +12959,7 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -12906,11 +12972,7 @@
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>SUZUKI GRAND VITARA 1.5 HIBRIDO</t>
-        </is>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -12968,17 +13030,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F135" t="n">
         <v>2026</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>21006</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>105022</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -12986,7 +13048,7 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -13057,14 +13119,14 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F136" t="n">
         <v>2026</v>
       </c>
       <c r="G136" t="n">
-        <v>494</v>
+        <v>23854</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -13075,7 +13137,7 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -13236,8 +13298,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
-        <v>2027</v>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PGC2026-pendiente</t>
+        </is>
       </c>
       <c r="B138" t="n">
         <v>137</v>
@@ -13261,10 +13325,10 @@
         <v>2012</v>
       </c>
       <c r="G138" t="n">
-        <v>357896</v>
+        <v>378142</v>
       </c>
       <c r="H138" t="n">
-        <v>18527332</v>
+        <v>19045903</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -13272,11 +13336,11 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -13286,7 +13350,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema de escape y sensores </t>
+          <t>Problemas en Sistema de escape, sensores y otras por antigüedad y kilometraje</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -13355,16 +13419,26 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>2026</v>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+      <c r="G139" t="n">
+        <v>11982</v>
+      </c>
+      <c r="H139" t="n">
+        <v>349020</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>11</v>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -13443,10 +13517,10 @@
         <v>2013</v>
       </c>
       <c r="G140" t="n">
-        <v>255241</v>
+        <v>260682</v>
       </c>
       <c r="H140" t="n">
-        <v>10788280</v>
+        <v>12213424</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -13468,7 +13542,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Varias y la antigüedad</t>
+          <t>Problema en la caja de cambio, iluminación, gases, amortiguación</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -13547,10 +13621,10 @@
         <v>2013</v>
       </c>
       <c r="G141" t="n">
-        <v>203230</v>
+        <v>208205</v>
       </c>
       <c r="H141" t="n">
-        <v>8344281</v>
+        <v>9338973</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -13558,7 +13632,7 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -13639,17 +13713,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Camioneta 4x2</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F142" t="n">
         <v>2015</v>
       </c>
       <c r="G142" t="n">
-        <v>239306</v>
+        <v>251851</v>
       </c>
       <c r="H142" t="n">
-        <v>12224018</v>
+        <v>12526765</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -13657,7 +13731,7 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -13671,7 +13745,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">En taller falla DPF (segunda reparación por mismo motivo)+ mantenimiento  general </t>
+          <t xml:space="preserve">Falla periodica de  DPF + mantenimiento  general </t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -13743,10 +13817,10 @@
         <v>2016</v>
       </c>
       <c r="G143" t="n">
-        <v>201668</v>
+        <v>221775</v>
       </c>
       <c r="H143" t="n">
-        <v>17442109</v>
+        <v>19687318</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -13766,7 +13840,11 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Problema en motor, en determinadas circunstacia el motor pierde fuerza </t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr">
         <is>
           <t>Se requiere renovación producto de la antigüedad y obsolecencia del vehículo el cual puede ser un riesgo para los pasajeros</t>
@@ -13836,10 +13914,10 @@
         <v>2016</v>
       </c>
       <c r="G144" t="n">
-        <v>210458</v>
+        <v>223772</v>
       </c>
       <c r="H144" t="n">
-        <v>14186947</v>
+        <v>16241781</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -13847,7 +13925,7 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -13927,10 +14005,10 @@
         <v>2017</v>
       </c>
       <c r="G145" t="n">
-        <v>208024</v>
+        <v>222347</v>
       </c>
       <c r="H145" t="n">
-        <v>6818346</v>
+        <v>7716606</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -13938,7 +14016,7 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -14016,10 +14094,10 @@
         <v>2018</v>
       </c>
       <c r="G146" t="n">
-        <v>198075</v>
+        <v>210242</v>
       </c>
       <c r="H146" t="n">
-        <v>9359182</v>
+        <v>11159938</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -14027,7 +14105,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -14098,17 +14176,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Minibus</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G147" t="n">
-        <v>125414</v>
+        <v>135277</v>
       </c>
       <c r="H147" t="n">
-        <v>4168996</v>
+        <v>4510707</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -14116,7 +14194,7 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -14128,12 +14206,20 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Problema en la regulación/actuación del turbocompresor y sistema de aditivación de carburante</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Producto de esta falla, se esta gestionando el envío del vehículo para un diagnóstico al taller de mantención de la concesionaria de la marca Peugeot en Puerto Montt.</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -14152,7 +14238,7 @@
         </is>
       </c>
       <c r="T147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -14194,10 +14280,10 @@
         <v>2020</v>
       </c>
       <c r="G148" t="n">
-        <v>124595</v>
+        <v>148653</v>
       </c>
       <c r="H148" t="n">
-        <v>5181172</v>
+        <v>5661782</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -14205,7 +14291,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -14283,10 +14369,10 @@
         <v>2025</v>
       </c>
       <c r="G149" t="n">
-        <v>21655</v>
+        <v>31971</v>
       </c>
       <c r="H149" t="n">
-        <v>361834</v>
+        <v>783190</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -14365,25 +14451,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F150" t="n">
         <v>2020</v>
       </c>
       <c r="G150" t="n">
-        <v>80967</v>
-      </c>
-      <c r="H150" t="n">
-        <v>13000000</v>
-      </c>
+        <v>94152</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Bencinero</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -14392,17 +14476,17 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Vehiculo con un siniestro en al año 2022 que afecto parte delantera derecha con un monto de arreglo de M$ 8.500 pagado por Aseguradora y con posteriores arreglos en la misma seccion del vehiculo por otros M$ 11.000</t>
+          <t>Sin fallas</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Vehiculo con un siniestro en al año 2022 que afecto parte delantera derecha con un monto de arreglo de M$ 8.500 pagado por Aseguradora y con posteriores arreglos en la misma seccion del vehiculo por otros M$ 11.000</t>
+          <t>Vehiculo en buen estado</t>
         </is>
       </c>
       <c r="O150" t="inlineStr"/>
@@ -14413,12 +14497,12 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -14427,7 +14511,7 @@
         </is>
       </c>
       <c r="T150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -14466,17 +14550,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F151" t="n">
         <v>2017</v>
       </c>
       <c r="G151" t="n">
-        <v>242894</v>
+        <v>253875</v>
       </c>
       <c r="H151" t="n">
-        <v>10000000</v>
+        <v>33248519</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -14484,11 +14568,11 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -14498,20 +14582,15 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Vehiculo con mas de  8 años de uso en carreteras de la Region de aysen, ripio y caminos de penetracion. Ya  requiere ser repuestapor una de similares caracteristicas y modelo</t>
+          <t>Sin fallas</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Vehiculo con mas de  8 años de uso en carreteras de la Region de aysen, ripio y caminos de penetracion. Ya  requiere ser repuestapor una de similares caracteristicas y modelo</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Es el vehiculo más antiguo, alto gasto en mantención y alto kilmetraje.
-Uso en carreteras de ripio y caminos de dificil acceso.</t>
-        </is>
-      </c>
+          <t>Vehiculo , sin fallas pero en proceso de baja</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -14568,25 +14647,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>2024</v>
       </c>
       <c r="G152" t="n">
-        <v>59239</v>
-      </c>
-      <c r="H152" t="n">
-        <v>2700000</v>
-      </c>
+        <v>75563</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Petrolero</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -14598,8 +14675,16 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Sin fallas</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Vehiculo , sin fallas pero activo</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -14657,25 +14742,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F153" t="n">
         <v>2024</v>
       </c>
       <c r="G153" t="n">
-        <v>39112</v>
-      </c>
-      <c r="H153" t="n">
-        <v>1500000</v>
-      </c>
+        <v>64646</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Petrolero</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -14687,8 +14770,16 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Sin fallas</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Vehiculo , sin fallas pero activo</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -14746,25 +14837,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F154" t="n">
         <v>2025</v>
       </c>
       <c r="G154" t="n">
-        <v>10646</v>
-      </c>
-      <c r="H154" t="n">
-        <v>500000</v>
-      </c>
+        <v>91981</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Petrolero</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -14776,8 +14865,16 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Sin fallas</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Vehiculo , sin fallas pero activo</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -14835,25 +14932,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F155" t="n">
         <v>2026</v>
       </c>
       <c r="G155" t="n">
-        <v>4600</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0</v>
-      </c>
+        <v>10557</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Bencinero</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -14865,8 +14960,16 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Sin fallas</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Vehiculo , sin fallas bero activo</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -14924,25 +15027,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>2026</v>
       </c>
       <c r="G156" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
-      </c>
+        <v>26627</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Petrolero</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -14954,8 +15055,16 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Sin fallas</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Vehiculo , sin fallas pero activo</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -15022,7 +15131,7 @@
         <v>2011</v>
       </c>
       <c r="G157" t="n">
-        <v>69928</v>
+        <v>73636</v>
       </c>
       <c r="H157" t="n">
         <v>2989054</v>
@@ -15032,9 +15141,7 @@
           <t>Petrolero</t>
         </is>
       </c>
-      <c r="J157" t="n">
-        <v>12</v>
-      </c>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -15042,14 +15149,10 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>Deterioro en carrocería y motor debido a la cantidad de años que se ha utilizado.  Preocupa la seguridad de los funcionarios, ya que el vehículo ha cumplido su vida útil hace 6 años</t>
-        </is>
-      </c>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>Fallas varias debido a los años de uso. Cumplió su vida útil año 2019</t>
@@ -15068,7 +15171,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -15082,7 +15185,7 @@
         </is>
       </c>
       <c r="T157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -15101,10 +15204,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>PGC 2026-comprado</t>
-        </is>
+      <c r="A158" t="n">
+        <v>2030</v>
       </c>
       <c r="B158" t="n">
         <v>157</v>
@@ -15116,24 +15217,32 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VLFL55</t>
+          <t>FKCW52</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
+        <v>2013</v>
+      </c>
+      <c r="G158" t="n">
+        <v>113076</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3740735</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -15142,11 +15251,15 @@
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Fallas varias debido a los años de uso. Cumplió su vida útil año 2021</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -15161,11 +15274,11 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -15184,8 +15297,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
-        <v>2030</v>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PGC2026-pendiente</t>
+        </is>
       </c>
       <c r="B159" t="n">
         <v>158</v>
@@ -15197,7 +15312,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>FKCW52</t>
+          <t>FKDY46</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -15209,22 +15324,20 @@
         <v>2013</v>
       </c>
       <c r="G159" t="n">
-        <v>107147</v>
+        <v>131982</v>
       </c>
       <c r="H159" t="n">
-        <v>3740735</v>
+        <v>6325700</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
           <t>Bencinero</t>
         </is>
       </c>
-      <c r="J159" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -15234,7 +15347,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Deterioro en carrocería y motor debido a la cantidad de años que se ha utilizado.  Preocupa la seguridad de los funcionarios, ya que el vehículo ha cumplido su vida útil hace  4 años</t>
+          <t>Problemas con el eje, cuyo repuesto no se ha encontrado en Chile. Problemas con la tapa del combustible</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -15255,7 +15368,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -15264,11 +15377,11 @@
         </is>
       </c>
       <c r="T159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
@@ -15284,7 +15397,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B160" t="n">
         <v>159</v>
@@ -15296,7 +15409,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>FKDY46</t>
+          <t>FKCW49</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -15308,19 +15421,17 @@
         <v>2013</v>
       </c>
       <c r="G160" t="n">
-        <v>127779</v>
+        <v>83394</v>
       </c>
       <c r="H160" t="n">
-        <v>6325700</v>
+        <v>3719334</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
           <t>Bencinero</t>
         </is>
       </c>
-      <c r="J160" t="n">
-        <v>9</v>
-      </c>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -15328,15 +15439,10 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Problemas con el eje, no existe repuesto en Punta Arenas, y se consultó con un taller mecánico que cotizó en Santiago y tampoco encontró. De acuerdo con lo señalado por el taller, sí se puede manejar, pero en cualquier momento podría falalr definitivamente.
-</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>Fallas varias debido a los años de uso. Cumplió su vida útil año 2021</t>
@@ -15355,25 +15461,25 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T160" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
@@ -15389,7 +15495,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B161" t="n">
         <v>160</v>
@@ -15401,7 +15507,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>FKCW49</t>
+          <t>JFTD73</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -15410,22 +15516,20 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="G161" t="n">
-        <v>78724</v>
+        <v>107968</v>
       </c>
       <c r="H161" t="n">
-        <v>3207734</v>
+        <v>2162023</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
           <t>Bencinero</t>
         </is>
       </c>
-      <c r="J161" t="n">
-        <v>9</v>
-      </c>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -15433,13 +15537,13 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Fallas varias debido a los años de uso. Cumplió su vida útil año 2021</t>
+          <t>Fallas varias debido a los años de uso.</t>
         </is>
       </c>
       <c r="O161" t="inlineStr"/>
@@ -15450,7 +15554,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -15460,7 +15564,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15483,9 +15587,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
-        <v>2029</v>
-      </c>
+      <c r="A162" t="inlineStr"/>
       <c r="B162" t="n">
         <v>161</v>
       </c>
@@ -15496,31 +15598,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>JFTD73</t>
+          <t>LVDS60</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SUV</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="G162" t="n">
-        <v>96344</v>
+        <v>21217</v>
       </c>
       <c r="H162" t="n">
-        <v>1828923</v>
+        <v>2047153</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Bencinero</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>8.5</v>
-      </c>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -15528,7 +15628,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
@@ -15540,7 +15640,7 @@
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -15559,7 +15659,7 @@
         </is>
       </c>
       <c r="T162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
@@ -15589,31 +15689,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LVDS60</t>
+          <t>TRCB88</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G163" t="n">
-        <v>20260</v>
+        <v>12682</v>
       </c>
       <c r="H163" t="n">
-        <v>2047153</v>
+        <v>333200</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
           <t>Petrolero</t>
         </is>
       </c>
-      <c r="J163" t="n">
-        <v>16</v>
-      </c>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -15625,11 +15723,7 @@
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>Fallas varias debido a los años de uso.</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -15682,31 +15776,27 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>TRCB88</t>
+          <t>VCSW12</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Camioneta 4x4</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G164" t="n">
-        <v>6867</v>
-      </c>
-      <c r="H164" t="n">
-        <v>333200</v>
-      </c>
+        <v>2978</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Petrolero</t>
-        </is>
-      </c>
-      <c r="J164" t="n">
-        <v>11.5</v>
-      </c>
+          <t>Híbrido</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -15760,7 +15850,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
       <c r="B165" t="n">
         <v>164</v>
       </c>
@@ -15771,34 +15865,30 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VCSW12</t>
+          <t>VYFL55</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G165" t="n">
-        <v>141</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
+        <v>2040</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Híbrido</t>
-        </is>
-      </c>
-      <c r="J165" t="n">
-        <v>18.5</v>
-      </c>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -15874,10 +15964,10 @@
         <v>2010</v>
       </c>
       <c r="G166" t="n">
-        <v>113540</v>
+        <v>118933</v>
       </c>
       <c r="H166" t="n">
-        <v>4068318</v>
+        <v>4418902</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -15885,7 +15975,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -15894,13 +15984,17 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>antigüedad/restricción vehicular</t>
+        </is>
+      </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente. Requiriendo altos costos en reparación y mantención</t>
         </is>
       </c>
       <c r="O166" t="inlineStr"/>
@@ -15911,7 +16005,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -15925,7 +16019,7 @@
         </is>
       </c>
       <c r="T166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -15962,17 +16056,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F167" t="n">
         <v>2012</v>
       </c>
       <c r="G167" t="n">
-        <v>197997</v>
+        <v>204930</v>
       </c>
       <c r="H167" t="n">
-        <v>5596662</v>
+        <v>5341800</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -15980,7 +16074,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -15994,12 +16088,12 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>presenta fallas diversas por alto kilometraje</t>
+          <t>Alto kilometraje- antigüedad</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>presenta fallas diversas por alto kilometraje</t>
+          <t>vehiculo tipo van para 8 pasajeros, vehiculo del año 2012, kilometraje avanzado, comienza a presentar fallas graves por antigüedad, no existe otro vehiculo de estas caractericticas en nustra dotacion asignada</t>
         </is>
       </c>
       <c r="O167" t="inlineStr"/>
@@ -16061,17 +16155,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F168" t="n">
         <v>2012</v>
       </c>
       <c r="G168" t="n">
-        <v>136352</v>
+        <v>138622</v>
       </c>
       <c r="H168" t="n">
-        <v>2569575</v>
+        <v>2331000</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -16079,7 +16173,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -16091,10 +16185,14 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>sin fallas</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>presenta fallas diversas por alto kilometraje</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente. Requiriendo altos costos en reparación y mantención, centro recreacional los vilos</t>
         </is>
       </c>
       <c r="O168" t="inlineStr"/>
@@ -16158,16 +16256,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Camioneta 4X4</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F169" t="n">
         <v>2026</v>
       </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" t="n">
+        <v>51</v>
+      </c>
       <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>10</v>
+      </c>
       <c r="K169" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -16178,8 +16284,16 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>no presentan fallas</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Vehículo en buenas condiciones.</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -16237,17 +16351,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Camion</t>
+          <t>Camión</t>
         </is>
       </c>
       <c r="F170" t="n">
         <v>2013</v>
       </c>
       <c r="G170" t="n">
-        <v>50805</v>
+        <v>53416</v>
       </c>
       <c r="H170" t="n">
-        <v>2463806</v>
+        <v>8006793</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -16255,7 +16369,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -16264,13 +16378,17 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>sin fallas</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>Vehículo activo en buenas condiciones y el gasto es mantenciones preventivas normales.</t>
         </is>
       </c>
       <c r="O170" t="inlineStr"/>
@@ -16286,7 +16404,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -16295,7 +16413,7 @@
         </is>
       </c>
       <c r="T170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
@@ -16332,34 +16450,40 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F171" t="n">
         <v>2012</v>
       </c>
       <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
+      <c r="H171" t="n">
+        <v>5304000</v>
+      </c>
       <c r="I171" t="inlineStr">
         <is>
           <t>Petrolero</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>vehiculo entregado en comodato precario parque metropolitano</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>No indica</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>vehiculo entregado en comodato precario parque metropolitano</t>
+          <t>Limpieza válvula EGR .</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Comodato</t>
+          <t>Antigüedad y kilometraje. Este vehículo esta entregado en comodato precario a Parque metropolitano desde el 03-08-2023. ( Se entregó con 160.000 de kilometraje).</t>
         </is>
       </c>
       <c r="O171" t="inlineStr"/>
@@ -16375,7 +16499,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -16384,7 +16508,7 @@
         </is>
       </c>
       <c r="T171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
@@ -16421,17 +16545,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F172" t="n">
         <v>2013</v>
       </c>
       <c r="G172" t="n">
-        <v>198951</v>
+        <v>211162</v>
       </c>
       <c r="H172" t="n">
-        <v>4049902</v>
+        <v>5196795</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -16439,22 +16563,26 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>problemas de motor y caja de cambio</t>
+        </is>
+      </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>problemas en sistema de valvula EGR, problemas en filtro de particulas DPF caja de cambio defectuosa, problemas de embrague</t>
         </is>
       </c>
       <c r="O172" t="inlineStr"/>
@@ -16465,12 +16593,12 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -16479,11 +16607,11 @@
         </is>
       </c>
       <c r="T172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
@@ -16516,17 +16644,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F173" t="n">
         <v>2013</v>
       </c>
       <c r="G173" t="n">
-        <v>202132</v>
+        <v>219093</v>
       </c>
       <c r="H173" t="n">
-        <v>2700855</v>
+        <v>4176500</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -16534,7 +16662,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -16543,17 +16671,17 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>Limpieza de sistema DPF y válvula EGR.</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente.</t>
         </is>
       </c>
       <c r="O173" t="inlineStr"/>
@@ -16564,7 +16692,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -16578,7 +16706,7 @@
         </is>
       </c>
       <c r="T173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
@@ -16615,13 +16743,15 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F174" t="n">
         <v>2013</v>
       </c>
-      <c r="G174" t="inlineStr"/>
+      <c r="G174" t="n">
+        <v>130818</v>
+      </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
@@ -16629,20 +16759,24 @@
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>vehiculo entregado en comodato precario parque metropolitano</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>No indica</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>vehiculo entregado en comodato precario parque metropolitano</t>
+          <t>Limpieza de sistema DPF y válvula EGR.</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Comodato</t>
+          <t>Comodato Precario a Parque Metropolitano.</t>
         </is>
       </c>
       <c r="O174" t="inlineStr"/>
@@ -16663,11 +16797,11 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -16704,17 +16838,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F175" t="n">
         <v>2013</v>
       </c>
       <c r="G175" t="n">
-        <v>183058</v>
+        <v>185224</v>
       </c>
       <c r="H175" t="n">
-        <v>4009103</v>
+        <v>7235995</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -16722,7 +16856,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -16736,12 +16870,12 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en caja de cambio y embrague, sistema DPF</t>
+          <t>problemas de embrague</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en caja de cambio y embrague, sistema DPF</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente.</t>
         </is>
       </c>
       <c r="O175" t="inlineStr"/>
@@ -16757,7 +16891,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -16766,11 +16900,11 @@
         </is>
       </c>
       <c r="T175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
@@ -16803,17 +16937,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F176" t="n">
         <v>2013</v>
       </c>
       <c r="G176" t="n">
-        <v>200802</v>
+        <v>209630</v>
       </c>
       <c r="H176" t="n">
-        <v>5745084</v>
+        <v>5914799</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -16821,7 +16955,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -16830,13 +16964,17 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>problemas de embrague</t>
+        </is>
+      </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente.</t>
         </is>
       </c>
       <c r="O176" t="inlineStr"/>
@@ -16847,7 +16985,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -16861,11 +16999,11 @@
         </is>
       </c>
       <c r="T176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V176" t="inlineStr">
@@ -16898,17 +17036,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F177" t="n">
         <v>2013</v>
       </c>
       <c r="G177" t="n">
-        <v>185789</v>
+        <v>186040</v>
       </c>
       <c r="H177" t="n">
-        <v>5032640</v>
+        <v>15584851</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -16916,11 +17054,11 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -16930,20 +17068,15 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>problemas de motor y caja de cambio</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>Vehículo con mas de 8 años de antigüedad, alto kilometraje y alto gasto en mantención acumulado.
-Presenta problemas en el sistema DPF (Filtro de Partículas Diésel) .</t>
-        </is>
-      </c>
+          <t>problemas en sistema de valvula EGR, problemas en filtro de particulas DPF caja de cambio defectuosa, problemas de embrague</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -17002,17 +17135,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F178" t="n">
         <v>2013</v>
       </c>
       <c r="G178" t="n">
-        <v>194555</v>
+        <v>206497</v>
       </c>
       <c r="H178" t="n">
-        <v>5015262</v>
+        <v>5408440</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -17020,11 +17153,11 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>En proceso de baja</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -17034,12 +17167,12 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>problemas de cardan, valvula EGR, filto DPF</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>problemas en sistema de valvula EGR, problemas en filtro de particulas DPF, cardan defectuoso,  problemas de embrague</t>
         </is>
       </c>
       <c r="O178" t="inlineStr"/>
@@ -17101,17 +17234,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F179" t="n">
         <v>2015</v>
       </c>
       <c r="G179" t="n">
-        <v>191131</v>
+        <v>208409</v>
       </c>
       <c r="H179" t="n">
-        <v>3563413</v>
+        <v>7212360</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -17119,7 +17252,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -17131,10 +17264,14 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Limpieza de sistema DPF, válvula EGR y cambio de kit de embrague.</t>
+        </is>
+      </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente.</t>
         </is>
       </c>
       <c r="O179" t="inlineStr"/>
@@ -17150,7 +17287,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -17159,7 +17296,7 @@
         </is>
       </c>
       <c r="T179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -17196,17 +17333,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F180" t="n">
         <v>2015</v>
       </c>
       <c r="G180" t="n">
-        <v>211194</v>
+        <v>229415</v>
       </c>
       <c r="H180" t="n">
-        <v>5863375</v>
+        <v>7523259</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -17214,7 +17351,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -17223,13 +17360,17 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Limpieza de sistema DPF y válvula EGR. Descarbonizado de admision </t>
+        </is>
+      </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente.</t>
         </is>
       </c>
       <c r="O180" t="inlineStr"/>
@@ -17240,7 +17381,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -17254,11 +17395,11 @@
         </is>
       </c>
       <c r="T180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
@@ -17291,17 +17432,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F181" t="n">
         <v>2015</v>
       </c>
       <c r="G181" t="n">
-        <v>195484</v>
+        <v>208720</v>
       </c>
       <c r="H181" t="n">
-        <v>3863388</v>
+        <v>6313382</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -17309,7 +17450,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -17318,17 +17459,17 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>Limpieza de sistema DPF y válvula EGR.</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>vehiculo presenta fallas en sistema DPF y valvula EGR</t>
+          <t>Antigüedad y alto kilometraje asociado. Derivado de estos dos factores, presentan fallas recurrentemente.</t>
         </is>
       </c>
       <c r="O181" t="inlineStr"/>
@@ -17339,12 +17480,12 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -17353,11 +17494,11 @@
         </is>
       </c>
       <c r="T181" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
@@ -17390,17 +17531,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F182" t="n">
         <v>2016</v>
       </c>
       <c r="G182" t="n">
-        <v>141461</v>
+        <v>157997</v>
       </c>
       <c r="H182" t="n">
-        <v>2050331</v>
+        <v>4872468</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -17408,7 +17549,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -17420,10 +17561,14 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>reparación tensor y correa</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>Vehículo en buen estado.</t>
         </is>
       </c>
       <c r="O182" t="inlineStr"/>
@@ -17492,10 +17637,10 @@
         <v>2019</v>
       </c>
       <c r="G183" t="n">
-        <v>86138</v>
+        <v>100980</v>
       </c>
       <c r="H183" t="n">
-        <v>1395922</v>
+        <v>1974600</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -17503,7 +17648,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -17512,13 +17657,17 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>no presenta fallas, solo desgaste por uso.</t>
+        </is>
+      </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>Vehículo en buenas condiciones.</t>
         </is>
       </c>
       <c r="O183" t="inlineStr"/>
@@ -17539,11 +17688,11 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
@@ -17582,17 +17731,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F184" t="n">
         <v>2020</v>
       </c>
       <c r="G184" t="n">
-        <v>70057</v>
+        <v>82570</v>
       </c>
       <c r="H184" t="n">
-        <v>1549539</v>
+        <v>2187400</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -17609,13 +17758,17 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>no presenta fallas, solo desgaste por uso.</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Antigüedad</t>
+          <t>Vehículo en buenas condiciones.</t>
         </is>
       </c>
       <c r="O184" t="inlineStr"/>
@@ -17670,22 +17823,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>TVFT21</t>
+          <t>TVFV21</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F185" t="n">
         <v>2025</v>
       </c>
       <c r="G185" t="n">
-        <v>9775</v>
+        <v>24400</v>
       </c>
       <c r="H185" t="n">
-        <v>273072</v>
+        <v>632977</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -17693,7 +17846,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -17707,10 +17860,14 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>gastos de mantención por resguardo de garantía</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
+          <t>no presentan fallas</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Vehículo en buenas condiciones.</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -17768,17 +17925,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F186" t="n">
         <v>2025</v>
       </c>
       <c r="G186" t="n">
-        <v>14200</v>
+        <v>32960</v>
       </c>
       <c r="H186" t="n">
-        <v>273072</v>
+        <v>633099</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -17786,7 +17943,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -17800,10 +17957,14 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>gastos de mantención por resguardo de garantía</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
+          <t>no presentan fallas</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Vehículo en buenas condiciones.</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
@@ -17861,25 +18022,31 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F187" t="n">
         <v>2026</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>11897</v>
       </c>
       <c r="H187" t="n">
-        <v>0</v>
+        <v>261505</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
           <t>Petrolero</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+      <c r="J187" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>Baja</t>
@@ -17887,10 +18054,14 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Vehículo sin movimiento a la espera de documentos del seguro contra terceros</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+          <t>no presentan fallas</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Vehículo en buenas condiciones.</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
@@ -18891,29 +19062,51 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VWCL81</t>
+          <t>VSHH24</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F200" t="n">
         <v>2026</v>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>8943</v>
+      </c>
+      <c r="H200" t="n">
+        <v>261505</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>no presentan fallas</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Vehículo en buenas condiciones.</t>
+        </is>
+      </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
@@ -18955,36 +19148,54 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
       <c r="B201" t="n">
         <v>200</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SERVIU Metropolitana</t>
+          <t>SERVIU Los Ríos</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VSHH24</t>
+          <t>VVGL84</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F201" t="n">
         <v>2026</v>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
+      <c r="G201" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H201" t="n">
+        <v>273756</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Híbrido</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>18</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>No indica</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
@@ -19032,11 +19243,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PGC 2026-comprado</t>
+          <t>PGC2026-pendiente</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -19045,70 +19256,78 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VVGL84</t>
+          <t>KBPC35</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="G202" t="n">
-        <v>10000</v>
+        <v>300000</v>
       </c>
       <c r="H202" t="n">
-        <v>273756</v>
+        <v>8637487</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Híbrido</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J202" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Problemas en Radiador y Caliper</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>8 AÑOS DE USO, se sugiere reemplazo por vehiculo cerrado (de preferencia SUV) ha presentando fallas en el radiador de calefaccion en varias ocaciones, generando un gasto mas alto en reparaciones.</t>
+        </is>
+      </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T202" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
@@ -19123,13 +19342,9 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>PGC2026-pendiente</t>
-        </is>
-      </c>
+      <c r="A203" t="inlineStr"/>
       <c r="B203" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -19138,22 +19353,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>KBPC35</t>
+          <t>LBXZ10</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G203" t="n">
-        <v>300000</v>
+        <v>230000</v>
       </c>
       <c r="H203" t="n">
-        <v>8637487</v>
+        <v>12150862</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -19175,15 +19390,19 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Problemas en Radiador y Caliper</t>
+          <t>ANTIGÜEDAD DE USO</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>8 AÑOS DE USO, se sugiere reemplazo por vehiculo cerrado (de preferencia SUV) ha presentando fallas en el radiador de calefaccion en varias ocaciones, generando un gasto mas alto en reparaciones.</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr"/>
+          <t xml:space="preserve">8 AÑOS DE USO, se sugiere reemplazo por vehiculo cerrado (de preferencia SUV) </t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Vehículo con mas de 8 años de antigüedad, alto kilometraje y alto gasto en mantención acumulado.</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -19226,7 +19445,7 @@
     <row r="204">
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -19235,30 +19454,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LBXZ10</t>
+          <t>LXFG48</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>Camioneta 4x2</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="G204" t="n">
-        <v>230000</v>
+        <v>60000</v>
       </c>
       <c r="H204" t="n">
-        <v>12150862</v>
+        <v>3343658</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J204" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -19272,45 +19491,41 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>ANTIGÜEDAD DE USO</t>
+          <t>NO APTO PARA LA REGION</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 AÑOS DE USO, se sugiere reemplazo por vehiculo cerrado (de preferencia SUV) </t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>Vehículo con mas de 8 años de antigüedad, alto kilometraje y alto gasto en mantención acumulado.</t>
-        </is>
-      </c>
+          <t>Tipo de vehículo NO Apto para la Region, se pierde la parte trasera del vehículo, no se pueden dejar cosas o trasladar, si esta lloviendo, se necesita un vehículo cerrado.</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
+          <t>no cumple</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
           <t>cumple</t>
         </is>
       </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T204" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
@@ -19327,7 +19542,7 @@
     <row r="205">
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -19336,30 +19551,30 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LXFG48</t>
+          <t>VBLY64</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CAMIONETA</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G205" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="H205" t="n">
-        <v>3343658</v>
+        <v>1437583</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Petrolero</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J205" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -19368,19 +19583,11 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>NO APTO PARA LA REGION</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>Tipo de vehículo NO Apto para la Region, se pierde la parte trasera del vehículo, no se pueden dejar cosas o trasladar, si esta lloviendo, se necesita un vehículo cerrado.</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
@@ -19389,7 +19596,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -19403,7 +19610,7 @@
         </is>
       </c>
       <c r="T205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
@@ -19424,31 +19631,31 @@
     <row r="206">
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SERVIU Los Ríos</t>
+          <t>SERVIU Arica y Parinacota</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VBLY64</t>
+          <t>LBXY16</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="G206" t="n">
-        <v>30000</v>
+        <v>95252</v>
       </c>
       <c r="H206" t="n">
-        <v>1437583</v>
+        <v>6652663</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -19456,7 +19663,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -19465,15 +19672,19 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>En diciembre 2026, el vehiculo cumple 08 años de adquisicion desde la fecha de su compra (según Factura).</t>
+        </is>
+      </c>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -19483,7 +19694,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
@@ -19492,7 +19703,7 @@
         </is>
       </c>
       <c r="T206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U206" t="inlineStr">
         <is>
@@ -19511,13 +19722,9 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>PGC 2026-Serviu-en proceso de compra</t>
-        </is>
-      </c>
+      <c r="A207" t="inlineStr"/>
       <c r="B207" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -19526,22 +19733,22 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>KCTK43</t>
+          <t>LVDS62</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMIONETA </t>
+          <t>Minibus</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G207" t="n">
-        <v>112343</v>
+        <v>53903</v>
       </c>
       <c r="H207" t="n">
-        <v>12875420</v>
+        <v>9631774</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -19549,7 +19756,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -19561,22 +19768,13 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>Tren delantero con fallas</t>
-        </is>
-      </c>
+      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
-          <t>El vehiculo, adquirido en 2018, se encuentra próximo a completar los 8 años de vida útil institucional. En su última mantención preventiva se detectó desgaste en los terminales de dirección, recomendándose el reemplazo de la bandeja inferior y superior, las bieletas y los axiales de dirección. Asimismo, ha requerido mantenciones correctivas de alto costo, lo que evidencia un deterioro propio de su antigüedad.</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>Es el vehículo con mas antigüedad del servicio, mayor kiloemtraje y gastos en mantención.
-David Alvarado mediante correo 30 abril 2026 solicita reempazo de este vehículo.</t>
-        </is>
-      </c>
+          <t>El Octubre de 2027, cumpliria 08 años de adquision desde la fecha de su compra (según Factura).</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>cumple</t>
@@ -19594,15 +19792,15 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T207" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
@@ -19619,7 +19817,7 @@
     <row r="208">
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -19628,30 +19826,30 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LBXY16</t>
+          <t>TLWS13</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="G208" t="n">
-        <v>88295</v>
+        <v>28233</v>
       </c>
       <c r="H208" t="n">
-        <v>4398435</v>
+        <v>0</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -19668,7 +19866,7 @@
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
@@ -19687,7 +19885,7 @@
         </is>
       </c>
       <c r="T208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
@@ -19708,7 +19906,7 @@
     <row r="209">
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -19717,30 +19915,30 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LVDS62</t>
+          <t>TTWV94</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">MINI BUS </t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G209" t="n">
-        <v>48533</v>
+        <v>23628</v>
       </c>
       <c r="H209" t="n">
-        <v>8571294</v>
+        <v>685280</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Petrolero</t>
+          <t>Bencinero</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -19749,21 +19947,11 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>Componente	                                    Problema
-Turbo VGT	                     Sucio, no apto para limpieza
-Solenoide de vacío del turbo Falla eléctrica</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>El vehículo, adquirido en 2020, se encuentra próximo a cumplir su vida útil institucional. Si bien actualmente no presenta fallas mecánicas relevantes, ha requerido mantenciones correctivas de alto costo, lo que refleja un desgaste propio de su antigüedad.</t>
-        </is>
-      </c>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
@@ -19777,7 +19965,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
@@ -19786,7 +19974,7 @@
         </is>
       </c>
       <c r="T209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
@@ -19805,9 +19993,13 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
       <c r="B210" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -19816,19 +20008,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>TLWS13</t>
+          <t>VZXR91</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMIIONETA </t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G210" t="n">
-        <v>18006</v>
+        <v>18</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -19838,12 +20030,10 @@
           <t>Petrolero</t>
         </is>
       </c>
-      <c r="J210" t="n">
-        <v>7</v>
-      </c>
+      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -19852,7 +20042,11 @@
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>“Vehículo nuevo, recientemente incorporado a la flota institucional. Actualmente se encuentra en proceso de gestión de alta.”</t>
+        </is>
+      </c>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
@@ -19896,39 +20090,39 @@
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SERVIU Arica y Parinacota</t>
+          <t>SERVIU Ñuble</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>TTWV94</t>
+          <t>TDBV10</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>STATION WAGON</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G211" t="n">
-        <v>13655</v>
+        <v>58963</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Bencinero</t>
+          <t>Petrolero</t>
         </is>
       </c>
       <c r="J211" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -19937,11 +20131,19 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>FALLAS POR DESGASTE Y USO</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Se prioriza la renovación del vehículo debido a las fallas recurrentes que ha presentado en diversos componentes y materiales. Si bien actualmente estas reparaciones han sido asumidas por la concesionaria, su recurrencia permite advertir un riesgo de mayores gastos de mantención y reparación para el Servicio una vez terminada dicha cobertura, además de eventuales períodos de indisponibilidad que podrían afectar la continuidad de las funciones institucionales.</t>
+        </is>
+      </c>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
@@ -19985,7 +20187,7 @@
     <row r="212">
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -19994,29 +20196,51 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>TDBV10</t>
+          <t>LYHF13</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Camioneta</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
+        <v>2020</v>
+      </c>
+      <c r="G212" t="n">
+        <v>164000</v>
+      </c>
+      <c r="H212" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>15</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>FALLAS POR DESGASTE , USO Y MATERIALES DEFECTUOSOS</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Se justifica la renovación del vehículo considerando su antigüedad y/o kilometraje acumulado, el incremento progresivo de las necesidades de mantención y la recurrencia de fallas asociadas al uso, proyectándose reparaciones de mayor costo, tales como intervención o reemplazo de componentes del sistema de embrague y otros elementos sujetos a desgaste. Adicionalmente, su motorización a bencina implica un mayor consumo de combustible respecto de alternativas más eficientes para las condiciones de operación institucional. Asimismo, al no contar con tracción 4x4, presenta limitaciones para el desplazamiento en sectores rurales y caminos de condiciones complejas de la Región de Ñuble. Por lo anterior, se recomienda su renovación por un vehículo que otorgue mayor eficiencia de combustible, confiabilidad mecánica y capacidad 4x4, acorde con las necesidades operacionales y territoriales del Servicio.</t>
+        </is>
+      </c>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
@@ -20025,7 +20249,7 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -20035,11 +20259,11 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -20060,7 +20284,7 @@
     <row r="213">
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -20069,29 +20293,51 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LYHF13</t>
+          <t>LYHF37</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Station wagon</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="F213" t="n">
         <v>2020</v>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
+      <c r="G213" t="n">
+        <v>167993</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>FALLAS POR DESGASTE Y USO</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Se justifica la renovación del vehículo considerando su antigüedad y/o kilometraje acumulado, el incremento progresivo de las necesidades de mantención y la recurrencia de fallas asociadas al uso, proyectándose reparaciones de mayor costo, tales como intervención o reemplazo de componentes del sistema de embrague y otros elementos sujetos a desgaste. Adicionalmente, su motorización a bencina implica un mayor consumo de combustible respecto de alternativas más eficientes para las condiciones de operación institucional. Asimismo, al no contar con tracción 4x4, presenta limitaciones para el desplazamiento en sectores rurales y caminos de condiciones complejas de la Región de Ñuble. Por lo anterior, se recomienda su renovación por un vehículo que otorgue mayor eficiencia de combustible, confiabilidad mecánica y capacidad 4x4, acorde con las necesidades operacionales y territoriales del Servicio.</t>
+        </is>
+      </c>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
@@ -20100,7 +20346,7 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -20110,11 +20356,11 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
@@ -20135,38 +20381,54 @@
     <row r="214">
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SERVIU Ñuble</t>
+          <t>Subsecretaría</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LYHF37</t>
+          <t>SZWZ80</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Station wagon</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="G214" t="n">
+        <v>90600</v>
+      </c>
+      <c r="H214" t="n">
+        <v>2508520</v>
+      </c>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>El vehículo ha tenido intervenciones menores como el cambio de bocina y su base, scanner y diagnóstico, reemplazo de sensores de oxígeno, cambio de bujías, mantención preventiva y sustitución de un neumático con balanceo. Estas reparaciones corresponden a fallas no críticas, propias del uso regular, sin evidenciar deterioro estructural ni gastos relevantes.</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>No se sugiere el cambio del vehículo, ya que las fallas son menores, el kilometraje es relativamente bajo y aún puede mantenerse operativo en el corto plazo, por lo que la prioridad de reemplazo es baja.</t>
+        </is>
+      </c>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
@@ -20210,7 +20472,7 @@
     <row r="215">
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -20219,22 +20481,22 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>SZWZ80</t>
+          <t>LVBP42</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>Van</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="G215" t="n">
-        <v>90600</v>
+        <v>132254</v>
       </c>
       <c r="H215" t="n">
-        <v>2508520</v>
+        <v>719950</v>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
@@ -20245,13 +20507,17 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>El vehículo ha tenido las siguientes intervenciones: Sistema de emisiones: desmontaje y montaje de sensores DPF, limpieza con productos especializados (Liqui Moly y limpiador DPF), y regeneración forzada con scanner. Sistema de control: revisión y reseteo de parámetros de presión de neumáticos. Mantenimiento preventivo: realizado a los 360.000 km y previamente a los 130.000 km. Estas acciones corresponden a fallas menores y mantenimientos preventivos, propios del desgaste normal por kilometraje, sin evidenciar deterioro estructural ni gastos relevantes.</t>
+        </is>
+      </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>No se sugiere el cambio del vehículo, ya que las fallas son menores, el kilometraje es relativamente bajo y aún puede mantenerse operativo en el corto plazo, por lo que la prioridad de reemplazo es baja.</t>
         </is>
       </c>
       <c r="O215" t="inlineStr"/>
@@ -20272,11 +20538,11 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
@@ -20297,7 +20563,7 @@
     <row r="216">
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -20306,7 +20572,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LVBP42</t>
+          <t>LVBP47</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -20318,10 +20584,10 @@
         <v>2020</v>
       </c>
       <c r="G216" t="n">
-        <v>132254</v>
+        <v>131786</v>
       </c>
       <c r="H216" t="n">
-        <v>849660</v>
+        <v>489090</v>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
@@ -20332,13 +20598,17 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M216" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>El vehículo ha presentado las siguientes intervenciones: Sistema eléctrico: cambio de batería 70 AMP Start-Stop. Mantenimiento preventivo: realizado a los 130.000 km. Estas acciones corresponden a ajustes menores y no críticos, propios del uso regular, sin evidenciar deterioro estructural ni gastos relevantes.</t>
+        </is>
+      </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>No se sugiere el cambio del vehículo, ya que las fallas son menores, el kilometraje es relativamente bajo y aún puede mantenerse operativo en el corto plazo, por lo que la prioridad de reemplazo es baja.</t>
         </is>
       </c>
       <c r="O216" t="inlineStr"/>
@@ -20384,7 +20654,7 @@
     <row r="217">
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -20393,22 +20663,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LVBP47</t>
+          <t>LZFS36</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Sedan</t>
         </is>
       </c>
       <c r="F217" t="n">
         <v>2020</v>
       </c>
       <c r="G217" t="n">
-        <v>131786</v>
+        <v>89544</v>
       </c>
       <c r="H217" t="n">
-        <v>489090</v>
+        <v>2150330</v>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
@@ -20419,13 +20689,17 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>El vehículo ha tenido intervenciones menores como desmontaje y montaje de parachoque delantero, cambio de bocina y su base, scanner y diagnóstico, reemplazo de sensores de oxígeno, cambio de bujías, mantención preventiva y sustitución de un neumático con balanceo. Estas reparaciones corresponden a fallas no críticas, propias del uso regular, sin evidenciar deterioro estructural ni gastos relevantes.</t>
+        </is>
+      </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>No se sugiere el cambio del vehículo, ya que las fallas son menores, el kilometraje es relativamente bajo y aún puede mantenerse operativo en el corto plazo, por lo que la prioridad de reemplazo es baja.</t>
         </is>
       </c>
       <c r="O217" t="inlineStr"/>
@@ -20446,11 +20720,11 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -20471,7 +20745,7 @@
     <row r="218">
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -20480,7 +20754,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LZFS36</t>
+          <t>JFSX57</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -20489,13 +20763,13 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="G218" t="n">
-        <v>89544</v>
+        <v>178837</v>
       </c>
       <c r="H218" t="n">
-        <v>2150330</v>
+        <v>980560</v>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
@@ -20506,19 +20780,23 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>El vehículo ha presentado las siguientes intervenciones: Neumáticos: cambio de 4 neumáticos 225/45 R17 y balanceo. Sistema eléctrico/motor: luz de check engine encendida, problemas de encendido y pérdida de fuerza; scanner y diagnóstico. Motor: cambio de bujías punta platino y borrado de código de falla. Sistema de lubricación: desmontaje y montaje de sensor de nivel de aceite, fijación de sensor suelto y reseteo con scanner. Mantenimiento preventivo: realizado a los 170.000 km. Estas reparaciones corresponden a fallas puntuales y no críticas, propias del desgaste normal por kilometraje, sin evidenciar deterioro estructural ni gastos relevantes.</t>
+        </is>
+      </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>No se sugiere el cambio del vehículo, ya que las fallas son menores, el kilometraje es relativamente bajo y aún puede mantenerse operativo en el corto plazo, por lo que la prioridad de reemplazo es baja.</t>
         </is>
       </c>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -20533,11 +20811,11 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -20558,7 +20836,7 @@
     <row r="219">
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -20567,22 +20845,22 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>JFSX57</t>
+          <t>HSXX73</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sedan</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="G219" t="n">
-        <v>178837</v>
+        <v>160413</v>
       </c>
       <c r="H219" t="n">
-        <v>1218560</v>
+        <v>1581510</v>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
@@ -20593,13 +20871,17 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>El vehículo ha presentado las siguientes intervenciones: Sistema de emisiones: cambio de catalítico alternativo. Sensores: reemplazo de dos sensores de oxígeno alternativos. Mantenimiento preventivo: realizado a los 150.000 km. Estas reparaciones corresponden a fallas puntuales y no críticas, propias del desgaste normal por kilometraje, sin evidenciar deterioro estructural ni un nivel de gasto significativo.</t>
+        </is>
+      </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>No se sugiere el cambio del vehículo, ya que las fallas son menores, el kilometraje es relativamente bajo y aún puede mantenerse operativo en el corto plazo, por lo que la prioridad de reemplazo es baja.</t>
         </is>
       </c>
       <c r="O219" t="inlineStr"/>
@@ -20645,7 +20927,7 @@
     <row r="220">
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -20654,22 +20936,22 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>HSXX73</t>
+          <t>HDRZ93</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>Sedan</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="G220" t="n">
-        <v>160413</v>
+        <v>306073</v>
       </c>
       <c r="H220" t="n">
-        <v>1581510</v>
+        <v>1338750</v>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
@@ -20680,13 +20962,17 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr"/>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Fallas recurrentes en sistemas críticos como el eléctrico (batería y botoneras), motor y emisiones (cambio de bujías, regeneración forzada del DPF), transmisión y diferencial (cardán y retén trasero), frenos (pastillas, calipers, discos y freno de mano), además de intervenciones en neumáticos, suspensión y aire acondicionado; todo esto refleja un desgaste avanzado y costos elevados, por lo que se sugiere su reemplazo con prioridad media, ya que aunque aún puede mantenerse operativo en el corto plazo, su confiabilidad y seguridad están comprometidas y los gastos seguirán aumentando.</t>
+        </is>
+      </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>Se sugiere el cambio del vehículo HD RZ. 93 por uno nuevo, pero con prioridad media. Esto significa que, si bien el reemplazo es recomendable para optimizar recursos y asegurar continuidad operativa, el nivel de urgencia no es inmediato como en otros casos de mayor gasto o fallas críticas. Puede mantenerse en operación a corto plazo, pero debe considerarse en el plan de renovación de flota.</t>
         </is>
       </c>
       <c r="O220" t="inlineStr"/>
@@ -20730,9 +21016,13 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PGC 2026-Subse-selico 228</t>
+        </is>
+      </c>
       <c r="B221" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -20741,22 +21031,22 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>HDRZ93</t>
+          <t>FKDX96</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sedan</t>
+          <t>Station Wagon</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="G221" t="n">
-        <v>306073</v>
+        <v>316001</v>
       </c>
       <c r="H221" t="n">
-        <v>1338750</v>
+        <v>1888530</v>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
@@ -20767,13 +21057,17 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Fallas en sistemas críticos Escape y DPF: regeneración forzada y modificación de programa, lo que refleja problemas en el sistema de emisiones.Transmisión y diferencial: desmontaje de cardán y cambio de retén trasero.Sistema eléctrico y accesorios: cambios de botoneras en las 4 puertas y adaptación del sistema eléctrico.Frenos: desmontaje de discos traseros, limpieza de balatas y regulación de freno de mano.Aire acondicionado: vacío y carga del sistema. Batería: problemas en bornes y necesidad de limpieza y reinstalación.</t>
+        </is>
+      </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>En la revisión de las mantenciones realizadas al vehículo Placa patente N° FK DX. 96, se observa que entre enero y julio del año 2026 se han efectuado reparaciones y servicios por un monto total de $1.888.530. Este gasto resulta significativamente elevado considerando las condiciones actuales del vehículo, cuyo año de fabricación corresponde a 2013 y que registra un kilometraje superior a los 300.000 km.</t>
         </is>
       </c>
       <c r="O221" t="inlineStr"/>
@@ -20784,7 +21078,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -20798,7 +21092,7 @@
         </is>
       </c>
       <c r="T221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -20817,13 +21111,9 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>PGC 2026-Subse-selico 228</t>
-        </is>
-      </c>
+      <c r="A222" t="inlineStr"/>
       <c r="B222" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -20832,22 +21122,22 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>FKDX96</t>
+          <t>FJZT19</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Station Wagon</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F222" t="n">
         <v>2013</v>
       </c>
       <c r="G222" t="n">
-        <v>316001</v>
+        <v>127788</v>
       </c>
       <c r="H222" t="n">
-        <v>1888530</v>
+        <v>0</v>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
@@ -20858,13 +21148,17 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>no presento fallas</t>
+        </is>
+      </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>No tiene movimiento y no ha tenido mantenciones entre oct 2025 y julio 2026</t>
         </is>
       </c>
       <c r="O222" t="inlineStr"/>
@@ -20910,7 +21204,7 @@
     <row r="223">
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -20919,22 +21213,22 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>FJZT19</t>
+          <t>FKDX99</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Camioneta 4x4</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F223" t="n">
         <v>2013</v>
       </c>
       <c r="G223" t="n">
-        <v>127788</v>
+        <v>348177</v>
       </c>
       <c r="H223" t="n">
-        <v>0</v>
+        <v>5453770</v>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
@@ -20945,13 +21239,17 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Fallas recurrentes en sistemas críticos Motor y turbo: reemplazo de turbo, sensor de presión y correas. Frenos y suspensión: múltiples cambios de discos, pastillas, calipers y amortiguadores. Sistema eléctrico y accesorios: batería, alternador, ampolletas, botones y telecomando. Sistema de refrigeración y aire acondicionado: bomba de agua, rodamiento y mantenciones mayores.</t>
+        </is>
+      </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>En la revisión de las mantenciones realizadas al vehículo Placa patente N°FK DX. 99, se observa que entre enero y julio del año 2026 se han efectuado reparaciones y servicios por un monto total de $5.401.410. Este gasto resulta significativamente elevado considerando las condiciones actuales del vehículo, cuyo año de fabricación corresponde a 2013 y que registra un kilometraje superior a los 300.000 km.</t>
         </is>
       </c>
       <c r="O223" t="inlineStr"/>
@@ -20962,12 +21260,12 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>si cumple</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
@@ -20976,11 +21274,11 @@
         </is>
       </c>
       <c r="T223" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
@@ -20997,7 +21295,7 @@
     <row r="224">
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -21006,22 +21304,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>FKDX99</t>
+          <t>DPRX61</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Suv</t>
+          <t>Station wagon</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="G224" t="n">
-        <v>348177</v>
+        <v>375046</v>
       </c>
       <c r="H224" t="n">
-        <v>5453770</v>
+        <v>5288360</v>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
@@ -21032,13 +21330,17 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M224" t="inlineStr"/>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Fallas recurrentes en sistemas clave: Frenos (discos, pastillas, caliper). Suspensión y dirección (bandejas, amortiguadores, alineaciones). Sistema eléctrico y accesorios (botones, telecomando, airbag). Aire acondicionado y alternador.</t>
+        </is>
+      </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>En la revisión de las mantenciones realizadas al vehículo Placa patente N° DP RX.61, se observa que entre enero y julio del año 2026 se han efectuado reparaciones y servicios por un monto total de $5.288.360. Este gasto resulta significativamente elevado considerando las condiciones actuales del vehículo, cuyo año de fabricación corresponde a 2012 y que registra un kilometraje superior a los 300.000 km.</t>
         </is>
       </c>
       <c r="O224" t="inlineStr"/>
@@ -21049,7 +21351,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -21063,11 +21365,11 @@
         </is>
       </c>
       <c r="T224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
@@ -21084,7 +21386,7 @@
     <row r="225">
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -21093,22 +21395,22 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>DPRX61</t>
+          <t>TVRT24</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Station wagon</t>
+          <t>Camioneta 4x4</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="G225" t="n">
-        <v>375046</v>
+        <v>24038</v>
       </c>
       <c r="H225" t="n">
-        <v>5581100</v>
+        <v>244990</v>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
@@ -21119,19 +21421,23 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M225" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>no presento fallas</t>
+        </is>
+      </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>El vehículo se mantiene en garantía y durante este año no ha presentado fallas relevantes. Las intervenciones realizadas corresponden únicamente a ajustes menores propios del uso regular, sin evidenciar deterioro estructural ni gastos significativos.</t>
         </is>
       </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -21141,16 +21447,16 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>si cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="T225" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -21171,7 +21477,7 @@
     <row r="226">
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -21180,22 +21486,22 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>TVRT24</t>
+          <t>VLJW54</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Camioneta 4x4</t>
+          <t>Suv</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G226" t="n">
-        <v>24038</v>
+        <v>15216</v>
       </c>
       <c r="H226" t="n">
-        <v>244990</v>
+        <v>261800</v>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
@@ -21206,13 +21512,17 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M226" t="inlineStr"/>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>no presento fallas</t>
+        </is>
+      </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Gasto mantención a partir de octubre 2025</t>
+          <t>El vehículo se mantiene en garantía y durante este año no ha presentado fallas relevantes. Las intervenciones realizadas corresponden únicamente a ajustes menores propios del uso regular, sin evidenciar deterioro estructural ni gastos significativos.</t>
         </is>
       </c>
       <c r="O226" t="inlineStr"/>
@@ -21250,89 +21560,6 @@
         </is>
       </c>
       <c r="W226" t="inlineStr">
-        <is>
-          <t>Catastro</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" t="n">
-        <v>227</v>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Subsecretaría</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>VLJW54</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Suv</t>
-        </is>
-      </c>
-      <c r="F227" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G227" t="n">
-        <v>15216</v>
-      </c>
-      <c r="H227" t="n">
-        <v>0</v>
-      </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="T227" t="n">
-        <v>0</v>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>catastro_vehiculos.xlsx</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
         <is>
           <t>Catastro</t>
         </is>
@@ -21384,7 +21611,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -21402,7 +21629,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -21420,7 +21647,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -21438,7 +21665,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -21456,7 +21683,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -21507,7 +21734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
@@ -21537,7 +21764,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -21567,7 +21794,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -21582,7 +21809,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -21596,7 +21823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21690,7 +21917,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21762,7 +21989,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -21836,7 +22063,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -21909,7 +22136,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -21973,7 +22200,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -22042,7 +22269,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -22114,7 +22341,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -22187,7 +22414,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>202</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -22257,7 +22484,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -22324,9 +22551,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -22386,6 +22617,267 @@
           <t>VSBB24</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SERVIU O'Higgins</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FKGK-55</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CAMIONETA</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2013</v>
+      </c>
+      <c r="G12" t="n">
+        <v>306271</v>
+      </c>
+      <c r="H12" t="n">
+        <v>14334928</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fallas electricas </t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>fallas electricas y antigüedad.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>WCXX86</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SERVIU O'Higgins</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HHRW-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Camioneta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2016</v>
+      </c>
+      <c r="G13" t="n">
+        <v>163484</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4028822</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 años de antigüedad </t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solo por años de antigüedad  </t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>WCXK88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PGC 2026-comprado</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SERVIU Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KC-TK-43</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMIONETA </t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2018</v>
+      </c>
+      <c r="G14" t="n">
+        <v>112343</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12875420</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Petrolero</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Tren delantero con fallas</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>El vehiculo, adquirido en 2018, se encuentra próximo a completar los 8 años de vida útil institucional. En su última mantención preventiva se detectó desgaste en los terminales de dirección, recomendándose el reemplazo de la bandeja inferior y superior, las bieletas y los axiales de dirección. Asimismo, ha requerido mantenciones correctivas de alto costo, lo que evidencia un deterioro propio de su antigüedad.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Es el vehículo con mas antigüedad del servicio, mayor kiloemtraje y gastos en mantención.
+David Alvarado mediante correo 30 abril 2026 solicita reempazo de este vehículo.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>KCTK43</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SERVIU Metropolitana</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JFDJ 70-6</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Camioneta 4x4</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G15" t="n">
+        <v>90433</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2847203</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Bencinero</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>vehiculo de baja mediante resolucion exenta 323 de 26.02.2026</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
